--- a/results/05_transient_transcription_output/508/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/508/original_transcribed_data.xlsx
@@ -766,7 +766,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -778,47 +778,46 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="n"/>
-      <c r="T4" s="3" t="inlineStr">
+          <t>8518</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">45
 </t>
         </is>
       </c>
+      <c r="T4" s="3" t="n"/>
       <c r="U4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
@@ -827,19 +826,25 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="n"/>
+          <t xml:space="preserve">2929
+</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -857,116 +862,139 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+1
+</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">317
+</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">243
+</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">153
+</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">316
+</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7072
+</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2929
+</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">262
 </t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">173
-</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12620
-</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">205
-</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="n"/>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">927
-</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="S5" s="3" t="n"/>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">702
-</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="X5" s="3" t="n"/>
       <c r="Y5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">68
@@ -987,131 +1015,135 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 5
-</t>
-        </is>
-      </c>
+      <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">914
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="n"/>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">7072
 </t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">507
-</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="n"/>
+          <t xml:space="preserve">812
+</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">42
+</t>
         </is>
       </c>
       <c r="Z6" s="3" t="n"/>
@@ -1128,95 +1160,100 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+1
+</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2305
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="n"/>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">316
+</t>
+        </is>
+      </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="n"/>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -1228,32 +1265,31 @@
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">413
 </t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="Z7" s="3" t="n"/>
@@ -1273,121 +1309,133 @@
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">458
+</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t xml:space="preserve">225
+</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>258</t>
+          <t xml:space="preserve">201
+</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1662
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -1408,126 +1456,122 @@
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1474
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
-</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n"/>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">578
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">578
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>452</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="n"/>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1909
-</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">43
+</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="n"/>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3186
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3822
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>73</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="Z9" s="3" t="n"/>
@@ -1547,122 +1591,127 @@
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">1424
+</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">876
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n"/>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">726
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15912
-</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="n"/>
+          <t xml:space="preserve">458
+</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1223
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="n"/>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
+          <t xml:space="preserve">488
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">386
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -1683,62 +1732,66 @@
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">896
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">437
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">421
 </t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="n"/>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>926</t>
+        </is>
+      </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>942</t>
         </is>
       </c>
       <c r="O11" s="3" t="n"/>
@@ -1750,55 +1803,55 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">3188
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -1819,119 +1872,131 @@
       <c r="C12" s="3" t="n"/>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">1122
+577
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="n"/>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">296
+</t>
+        </is>
+      </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">62
+</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t xml:space="preserve">84
+</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="S12" s="3" t="n"/>
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">612
+</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -1952,122 +2017,129 @@
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">183
 </t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="n"/>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>938</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">2627
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="U13" s="3" t="n"/>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>812</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -2088,37 +2160,37 @@
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">2824
 </t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -2130,31 +2202,31 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1929
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9043
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -2166,55 +2238,51 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1252
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">63
+</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="n"/>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1832
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">3
+</t>
         </is>
       </c>
       <c r="Z14" s="3" t="n"/>
@@ -2234,36 +2302,37 @@
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>165</t>
+          <t xml:space="preserve">983
+</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -2275,81 +2344,90 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1921
 </t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="n"/>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">1466
 </t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="U15" s="3" t="n"/>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2152
+</t>
+        </is>
+      </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">858
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">514
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -2370,124 +2448,122 @@
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>923</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9513
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9532
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">247
+</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="n"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t xml:space="preserve">922
+</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>266</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">429
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t xml:space="preserve">52
+</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18417
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -2508,113 +2584,132 @@
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">283
+</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4811
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="n"/>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="n"/>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2429
+</t>
+        </is>
+      </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">1466
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>266</t>
+          <t xml:space="preserve">57
+</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">91
+</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t xml:space="preserve">29
+</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8083
+          <t xml:space="preserve">853
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1510
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -2635,122 +2730,128 @@
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">481
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">953
+</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2456
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">686
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="T18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4921
+</t>
+        </is>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">22
 </t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="n"/>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2518
-</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
-      <c r="S18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="T18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">649
-</t>
-        </is>
-      </c>
-      <c r="U18" s="3" t="n"/>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">483
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
@@ -2771,125 +2872,132 @@
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t xml:space="preserve">241
+</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262622
+</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52
+</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="T19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">25
 </t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="n"/>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9812
-</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="T19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">942
-</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="V19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>2543</t>
+          <t xml:space="preserve">48
+</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2852
+          <t xml:space="preserve">8282
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="Z19" s="3" t="n"/>
@@ -2909,127 +3017,128 @@
       <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>468</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">090
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="n"/>
+          <t xml:space="preserve">857
+</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">686
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3050,127 +3159,133 @@
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2392
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">2139
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12922
+          <t xml:space="preserve">13932
 </t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">9272
 </t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
-        </is>
-      </c>
-      <c r="U21" s="3" t="n"/>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">292
+</t>
+        </is>
+      </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">903
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -3191,133 +3306,130 @@
       <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>381</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1842
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">00
 </t>
         </is>
       </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">929
-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1999
-</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1210
-</t>
-        </is>
-      </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1084
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">428
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -3338,131 +3450,131 @@
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">579
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>688</t>
+          <t xml:space="preserve">152
+</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">3894
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>962</t>
+          <t xml:space="preserve">38
+</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">939
+          <t xml:space="preserve">1851
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">13932
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">014
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>412</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5360
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">379
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1026
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1974
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4278
+          <t xml:space="preserve">2302
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Z23" s="3" t="n"/>
@@ -3482,122 +3594,125 @@
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32828
+</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">060
+</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">988
-</t>
-        </is>
-      </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">939
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3912
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">712
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">802
 </t>
         </is>
       </c>
@@ -3624,130 +3739,129 @@
       <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">1446
+</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>1832</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4978
+</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1022
+</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1221
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="T25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">342
+</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">63
+</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0926
+</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">21
 </t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5922
-</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3912
-</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="T25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">762
-</t>
-        </is>
-      </c>
-      <c r="U25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">59
-</t>
-        </is>
-      </c>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">245
-</t>
-        </is>
-      </c>
-      <c r="X25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">862
-</t>
-        </is>
-      </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">22 1
 </t>
         </is>
       </c>
@@ -3768,19 +3882,18 @@
       <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -3792,104 +3905,107 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="n"/>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">532
+</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="T26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">25
 </t>
         </is>
       </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5922
-</t>
-        </is>
-      </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="Q26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="T26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">632
-</t>
-        </is>
-      </c>
-      <c r="U26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="V26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="W26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="Z26" s="3" t="n"/>
@@ -3909,126 +4025,133 @@
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">19
 </t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="n"/>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">938
+</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1
 </t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="R27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2393
-</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2349
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>532</t>
+          <t xml:space="preserve">62
+</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>86</t>
+          <t xml:space="preserve">08
+</t>
         </is>
       </c>
       <c r="Z27" s="3" t="n"/>
@@ -4048,43 +4171,43 @@
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">391
+</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">158
 </t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4096,83 +4219,85 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19584
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1922
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">2
+</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">45
+</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8539
+</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>537</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">145
 </t>
-        </is>
-      </c>
-      <c r="T28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="U28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="V28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="W28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">298
-</t>
-        </is>
-      </c>
-      <c r="X28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">862
-</t>
-        </is>
-      </c>
-      <c r="Y28" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="Z28" s="3" t="n"/>
@@ -4192,13 +4317,13 @@
       <c r="C29" s="3" t="n"/>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1539
 </t>
         </is>
       </c>
@@ -4210,114 +4335,115 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">356
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">168
+</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26511
+          <t xml:space="preserve">16825
 </t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1902
+          <t xml:space="preserve">1928
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4516
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">64
+</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1042
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3826
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Z29" s="3" t="n"/>
@@ -4337,49 +4463,54 @@
       <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1494
+          <t xml:space="preserve">3061
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">43
+</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>588</t>
+          <t xml:space="preserve">12
+</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>896</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>06</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>05</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -4391,70 +4522,71 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">39086
+</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>264</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>264</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9222
+          <t xml:space="preserve">3222
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
+          <t xml:space="preserve">492
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">1346
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">10426
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">3225
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -4475,124 +4607,128 @@
       <c r="C31" s="3" t="n"/>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">896
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>582</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>806</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">21
 </t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">27511
 </t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">4526
 </t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t xml:space="preserve">1397
+</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">289
+</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>226444</t>
+          <t xml:space="preserve">253
+</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">482
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">635
 </t>
         </is>
       </c>
@@ -4613,73 +4749,90 @@
       <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t xml:space="preserve">47
+</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>86</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t xml:space="preserve">11
+</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">4
+</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">36
+</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>725</t>
+          <t xml:space="preserve">09
+</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11289
-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="n"/>
-      <c r="O32" s="3" t="n"/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">782
+</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>264</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">2829
 </t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4691,37 +4844,37 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">353
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">803
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -4742,98 +4895,96 @@
       <c r="C33" s="3" t="n"/>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139326
-</t>
+          <t>343</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
+          <t>4841</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1818
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11289
+          <t xml:space="preserve">1879
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1903
-</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="n"/>
+          <t xml:space="preserve">821
+</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">482
 </t>
         </is>
       </c>
@@ -4845,25 +4996,25 @@
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -4881,77 +5032,88 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n"/>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+3
+</t>
+        </is>
+      </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1321
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="n"/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
+          <t xml:space="preserve">782
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9282
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4963,19 +5125,18 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">682
+          <t xml:space="preserve">632
 </t>
         </is>
       </c>
@@ -4987,25 +5148,25 @@
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
+          <t xml:space="preserve">863
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
@@ -5026,128 +5187,121 @@
       <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="n"/>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+</t>
+        </is>
+      </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1922
-</t>
-        </is>
-      </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9282
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">7922
+</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="n"/>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>801</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2218
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="n"/>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">336
+          <t xml:space="preserve">535
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">451
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -5165,68 +5319,80 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n"/>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+3
+</t>
+        </is>
+      </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t xml:space="preserve">182
+</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="n"/>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180902
-</t>
-        </is>
-      </c>
-      <c r="O36" s="3" t="n"/>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">10
@@ -5241,49 +5407,49 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1306
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t>283</t>
+          <t xml:space="preserve">2973
+</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">1283
 </t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1299
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9676
+          <t xml:space="preserve">582
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">372
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Z36" s="3" t="n"/>
@@ -5303,68 +5469,75 @@
       <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1615
+          <t xml:space="preserve">2356
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3929
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>846344</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">39
+</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>203</t>
+          <t xml:space="preserve">13
+</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">499
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14418
+          <t xml:space="preserve">3
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09502
-</t>
-        </is>
-      </c>
-      <c r="O37" s="3" t="n"/>
+          <t xml:space="preserve">94503
+</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">902
+</t>
+        </is>
+      </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1428
@@ -5373,54 +5546,56 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t xml:space="preserve">122
+</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">488
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">903
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">12421
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">1252
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">2672
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">324
+</t>
         </is>
       </c>
       <c r="Z37" s="3" t="n"/>
@@ -5440,65 +5615,60 @@
       <c r="C38" s="3" t="n"/>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t xml:space="preserve">1615
+</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">3228
 </t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">499
+          <t xml:space="preserve">492
 </t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9811
-</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>883384</t>
-        </is>
-      </c>
+          <t xml:space="preserve">7857
+</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="n"/>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -5516,56 +5686,54 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">489
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">2852
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8216
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Z38" s="3" t="n"/>
@@ -5585,48 +5753,47 @@
       <c r="C39" s="3" t="n"/>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2516
+          <t xml:space="preserve">546
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>323</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5636,10 +5803,14 @@
 </t>
         </is>
       </c>
-      <c r="M39" s="3" t="n"/>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
@@ -5652,13 +5823,13 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -5670,7 +5841,7 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -5682,25 +5853,25 @@
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
+          <t xml:space="preserve">716
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1944
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -5718,131 +5889,135 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n"/>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">422
+</t>
+        </is>
+      </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
+          <t xml:space="preserve">941
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1983
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="n"/>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">472
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">2478
 </t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">869
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -5860,52 +6035,57 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n"/>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">422
+</t>
+        </is>
+      </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5915,35 +6095,45 @@
 </t>
         </is>
       </c>
-      <c r="M41" s="3" t="n"/>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="n"/>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -5955,25 +6145,25 @@
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">823
+          <t xml:space="preserve">869
 </t>
         </is>
       </c>
@@ -5997,63 +6187,58 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
+      <c r="C42" s="3" t="n"/>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">941
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -6065,62 +6250,67 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19221
+          <t xml:space="preserve">931
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41
+</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">720
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">22
 </t>
         </is>
       </c>
-      <c r="P42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="R42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">820
-</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
-      <c r="T42" s="3" t="n"/>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70
-</t>
-        </is>
-      </c>
-      <c r="V42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">5822
 </t>
         </is>
       </c>
@@ -6144,45 +6334,40 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
+      <c r="C43" s="3" t="n"/>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">1285
 </t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -6200,31 +6385,53 @@
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1789
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="n"/>
-      <c r="N43" s="3" t="n"/>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1142
+745
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225778
+22
+</t>
+        </is>
+      </c>
       <c r="O43" s="3" t="n"/>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="n"/>
-      <c r="R43" s="3" t="n"/>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">3
+6
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3819
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
@@ -6235,25 +6442,25 @@
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">957
+          <t xml:space="preserve">852
 </t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">963
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9272
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>243</t>
         </is>
       </c>
       <c r="Z43" s="3" t="n"/>
@@ -6273,47 +6480,51 @@
       <c r="C44" s="3" t="n"/>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1293
+          <t xml:space="preserve">4262
+7
 </t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
+          <t xml:space="preserve">442
 </t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">547
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t xml:space="preserve">7
+</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t xml:space="preserve">2429
+14
+</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">7
+7
 </t>
         </is>
       </c>
@@ -6321,45 +6532,44 @@
       <c r="M44" s="3" t="n"/>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13663
+          <t xml:space="preserve">77 777
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="n"/>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1069
-</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1029
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21213
+          <t xml:space="preserve">2418
 </t>
         </is>
       </c>
       <c r="T44" s="3" t="n"/>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -6371,14 +6581,13 @@
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">3272
 </t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>504</t>
         </is>
       </c>
       <c r="Z44" s="3" t="n"/>
@@ -6398,7 +6607,7 @@
       <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
@@ -6410,35 +6619,36 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">1929
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t xml:space="preserve">698
+</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>455</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">2828
 </t>
         </is>
       </c>
@@ -6454,29 +6664,35 @@
 </t>
         </is>
       </c>
-      <c r="N45" s="3" t="n"/>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">983
-</t>
-        </is>
-      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41272728
+1 8
+</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="n"/>
       <c r="P45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">06
 </t>
         </is>
       </c>
-      <c r="Q45" s="3" t="n"/>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">602
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -6491,7 +6707,7 @@
       <c r="W45" s="3" t="n"/>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 2
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
@@ -6510,7 +6726,12 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n"/>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 191
+</t>
+        </is>
+      </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">323
@@ -6519,89 +6740,90 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">3
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="n"/>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t xml:space="preserve">39
+</t>
         </is>
       </c>
       <c r="K46" s="3" t="n"/>
       <c r="L46" s="3" t="n"/>
       <c r="M46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+278
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">062
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="n"/>
+      <c r="R46" s="3" t="n"/>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">8
 </t>
         </is>
       </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="n"/>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="n"/>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="n"/>
-      <c r="T46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="U46" s="3" t="n"/>
+      <c r="T46" s="3" t="n"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12901
+</t>
+        </is>
+      </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2999
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="n"/>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9 2
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1501
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1999
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">749
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="n"/>
+      <c r="Y46" s="3" t="n"/>
       <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/508/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/508/original_transcribed_data.xlsx
@@ -729,7 +729,7 @@
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">917
 </t>
         </is>
       </c>
@@ -741,7 +741,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
@@ -766,7 +766,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">1829
 </t>
         </is>
       </c>
@@ -778,46 +778,50 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">916
 </t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">238
 </t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>8518</t>
-        </is>
-      </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="n"/>
+          <t xml:space="preserve">293
+</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>5452</t>
+        </is>
+      </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
@@ -826,28 +830,18 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2929
-</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="n"/>
+      <c r="Y4" s="3" t="n"/>
       <c r="Z4" s="3" t="n"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -862,40 +856,34 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-1
-</t>
-        </is>
-      </c>
+      <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -919,89 +907,90 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">2176
 </t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7072
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2929
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">1299
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="Z5" s="3" t="n"/>
+          <t xml:space="preserve">762
+</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>2</t>
@@ -1018,135 +1007,132 @@
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">342
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">0170
 </t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="n"/>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">916
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1175
+</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="n"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7072
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
+          <t xml:space="preserve">2074
 </t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>615</t>
+          <t xml:space="preserve">1144
+</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">212
+</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">2513
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="n"/>
+          <t xml:space="preserve">772
+</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -1160,136 +1146,126 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-1
-</t>
-        </is>
-      </c>
+      <c r="C7" s="3" t="n"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">2105
 </t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>152</t>
+          <t xml:space="preserve">106
+</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">1203
 </t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">316
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="n"/>
+      <c r="O7" s="3" t="n"/>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>013</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="n"/>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">816
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">413
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t xml:space="preserve">862
+</t>
         </is>
       </c>
       <c r="Z7" s="3" t="n"/>
@@ -1309,134 +1285,123 @@
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">458
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">2946
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="Z8" s="3" t="n"/>
@@ -1456,121 +1421,122 @@
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">1474
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">896
 </t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">1125
+</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">578
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">9578
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">096
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">9492
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>942</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="n"/>
+          <t xml:space="preserve">926
+</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="n"/>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14546
+</t>
+        </is>
+      </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="n"/>
+          <t xml:space="preserve">1294
+</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11109
+</t>
+        </is>
+      </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">3186
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">19488
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1269
+</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="n"/>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">2311
 </t>
         </is>
       </c>
@@ -1591,13 +1557,13 @@
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1424
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -1609,113 +1575,108 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">972
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">458
-</t>
-        </is>
-      </c>
+          <t>814</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="n"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>521</t>
+          <t xml:space="preserve">912
+</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="n"/>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
+          <t xml:space="preserve">1642
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">12822
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">386
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="n"/>
+          <t xml:space="preserve">2162
+</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1732,126 +1693,120 @@
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">437
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">421
-</t>
+          <t>483</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>93</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>942</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="O11" s="3" t="n"/>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3188
+          <t xml:space="preserve">1267
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">1612
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">1812
 </t>
         </is>
       </c>
@@ -1872,131 +1827,121 @@
       <c r="C12" s="3" t="n"/>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1122
-577
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="n"/>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">296
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="n"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">902
+</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">251
 </t>
         </is>
       </c>
-      <c r="S12" s="3" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">1612
 </t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>254</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1945
 </t>
         </is>
       </c>
@@ -2017,129 +1962,116 @@
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">104
+</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>938</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>464</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2627
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>430</t>
+          <t xml:space="preserve">142
+</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>812</t>
+          <t xml:space="preserve">1226
+</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">1852
 </t>
         </is>
       </c>
@@ -2160,128 +2092,126 @@
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">299
+</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1495
+</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1165
+</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>43414</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="n"/>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1214
+</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29234
+</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">582
+</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1252
+</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">264
 </t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2824
-</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1929
-</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">296
-</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63
-</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="n"/>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
+          <t xml:space="preserve">514
 </t>
         </is>
       </c>
@@ -2302,55 +2232,48 @@
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">983
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="n"/>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -2360,74 +2283,70 @@
 </t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
+      <c r="N15" s="3" t="n"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1466
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">382
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2152
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">853
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -2448,122 +2367,124 @@
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1408
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">923
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="n"/>
+          <t xml:space="preserve">946
+</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
+          <t xml:space="preserve">11823
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">1266
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">19492
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">11246
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">17088
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">11510
 </t>
         </is>
       </c>
@@ -2584,132 +2505,113 @@
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">1895
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">4129
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
+          <t xml:space="preserve">1188
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="n"/>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1912
+</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03
+</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="T17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">649
+</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="n"/>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">822
+</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2429
-</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1466
-</t>
-        </is>
-      </c>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="T17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="U17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="V17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="W17" s="3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="X17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">853
-</t>
-        </is>
-      </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -2730,128 +2632,120 @@
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>302</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">249
+</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">481
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>466</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2456
-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4110
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="n"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>03</t>
+          <t xml:space="preserve">2288
+</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">686
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1072
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="n"/>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t xml:space="preserve">260
+</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4921
+          <t xml:space="preserve">942
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">483
+          <t xml:space="preserve">852
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -2872,131 +2766,111 @@
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">29505
+</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">241
 </t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262622
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52
-</t>
-        </is>
-      </c>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="n"/>
+      <c r="N19" s="3" t="n"/>
+      <c r="O19" s="3" t="n"/>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">230
+</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8282
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -3017,128 +2891,114 @@
       <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>486</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="n"/>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">857
-</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
-      </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="n"/>
+      <c r="O20" s="3" t="n"/>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">686
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>324</t>
+          <t xml:space="preserve">262
+</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="U20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t xml:space="preserve">221
+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -3159,133 +3019,122 @@
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">1013
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2139
+          <t xml:space="preserve">738
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
-</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13932
-</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9272
-</t>
-        </is>
-      </c>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="n"/>
+      <c r="O21" s="3" t="n"/>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -3306,130 +3155,128 @@
       <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>381</t>
+          <t xml:space="preserve">298
+</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1842
-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="n"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">285
+</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">2399
+</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">9562
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1399
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">802
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1947
 </t>
         </is>
       </c>
@@ -3450,131 +3297,117 @@
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">11441
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">2904
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n"/>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3894
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">024644
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1851
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13932
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">14209
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="n"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">9316
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>412</t>
+          <t xml:space="preserve">11210
+</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">1072
+</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">93606
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">11084
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1026
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">1977
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2302
+          <t xml:space="preserve">09278
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>08</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="Z23" s="3" t="n"/>
@@ -3594,125 +3427,106 @@
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">18298
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32828
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">060
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="n"/>
+      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">939
-</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
+          <t>13164</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="n"/>
+      <c r="O24" s="3" t="n"/>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>3605</t>
+          <t xml:space="preserve">1239
+</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">7282
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
+          <t xml:space="preserve">852
 </t>
         </is>
       </c>
@@ -3739,129 +3553,127 @@
       <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1446
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1187
+</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">94
 </t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">53
-</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>1832</t>
-        </is>
-      </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>962</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>934</t>
+          <t xml:space="preserve">199
+</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4978
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="n"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">11922
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">1090
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221
-</t>
+          <t>430</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">342
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0926
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t xml:space="preserve">232
+</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">1692
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22 1
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -3882,18 +3694,19 @@
       <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t xml:space="preserve">296
+</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">1592
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -3905,106 +3718,98 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">19
+</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">2188
+</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>486</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">532
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="n"/>
+      <c r="N26" s="3" t="n"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">915
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">7162
 </t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">1862
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -4025,73 +3830,68 @@
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1974
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="n"/>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
-</t>
+          <t>494</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -4102,55 +3902,50 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="U27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="U27" s="3" t="n"/>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">1802
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -4171,132 +3966,126 @@
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1079
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1140
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>463</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1687
+</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="n"/>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">1190809
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8539
+          <t xml:space="preserve">402
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">5622
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>537</t>
+          <t xml:space="preserve">538
+</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -4317,13 +4106,13 @@
       <c r="C29" s="3" t="n"/>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1539
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
@@ -4335,67 +4124,62 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">356
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">1918
 </t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1892
 </t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16825
-</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1928
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1958
+</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="n"/>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
@@ -4407,25 +4191,25 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1394
 </t>
         </is>
       </c>
@@ -4437,13 +4221,14 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">1862
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="Z29" s="3" t="n"/>
@@ -4463,130 +4248,122 @@
       <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3061
+          <t xml:space="preserve">194984
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">896
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">588
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">806
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>05</t>
+          <t xml:space="preserve">313
+</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">2927
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39086
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="n"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>412</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>264</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">1207
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="S30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3222
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11123
+</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="n"/>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">492
+          <t xml:space="preserve">1538222
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1346
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10426
+          <t xml:space="preserve">11042
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3225
+          <t xml:space="preserve">3126
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">9284
 </t>
         </is>
       </c>
@@ -4607,128 +4384,116 @@
       <c r="C31" s="3" t="n"/>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">238
+</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>582</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>806</t>
+          <t xml:space="preserve">161
+</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n"/>
+      <c r="L31" s="3" t="n"/>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27511
-</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="n"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4526
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1826
+</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">253
 </t>
         </is>
       </c>
-      <c r="S31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">64
-</t>
-        </is>
-      </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">482
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">635
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -4749,135 +4514,124 @@
       <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">14183
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">782
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="n"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">12196
 </t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>264</t>
+          <t xml:space="preserve">04
+</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2829
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
-        </is>
-      </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">845
+</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="n"/>
       <c r="Z32" s="3" t="n"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -4895,73 +4649,70 @@
       <c r="C33" s="3" t="n"/>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>343</t>
+          <t xml:space="preserve">326
+</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">253
+</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t xml:space="preserve">945
+</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t xml:space="preserve">100
+</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1879
-</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">821
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="n"/>
+      <c r="N33" s="3" t="n"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -4972,49 +4723,49 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">482
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">1803
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1688
 </t>
         </is>
       </c>
@@ -5032,88 +4783,67 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-3
-</t>
-        </is>
-      </c>
+      <c r="C34" s="3" t="n"/>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">1921
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
+          <t xml:space="preserve">2418
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">935
 </t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">782
-</t>
-        </is>
-      </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="n"/>
+      <c r="N34" s="3" t="n"/>
+      <c r="O34" s="3" t="n"/>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">12825
 </t>
         </is>
       </c>
@@ -5125,48 +4855,48 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>209</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">632
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
+          <t xml:space="preserve">1863
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -5187,121 +4917,123 @@
       <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7922
-</t>
-        </is>
-      </c>
-      <c r="O35" s="3" t="n"/>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="n"/>
+      <c r="N35" s="3" t="n"/>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>801</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="n"/>
+          <t xml:space="preserve">280
+</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t>246</t>
+          <t xml:space="preserve">246
+</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">535
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">451
+          <t xml:space="preserve">2517
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">8320
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1628
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -5319,137 +5051,127 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-3
-</t>
-        </is>
-      </c>
+      <c r="C36" s="3" t="n"/>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1514
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="n"/>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
+      <c r="N36" s="3" t="n"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">12312
 </t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2973
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1283
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">582
+          <t xml:space="preserve">3852
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">115
+</t>
         </is>
       </c>
       <c r="Z36" s="3" t="n"/>
@@ -5469,132 +5191,127 @@
       <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356
+          <t xml:space="preserve">11615
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1269
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">0694
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">87110
+</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">422
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">9811
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">94503
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">9410
+</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="n"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">9506
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1428
 </t>
         </is>
       </c>
-      <c r="Q37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
+          <t xml:space="preserve">2413
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">903
+          <t xml:space="preserve">1009
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12421
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
+          <t xml:space="preserve">1299
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2672
+          <t xml:space="preserve">3672
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">372
 </t>
         </is>
       </c>
@@ -5615,119 +5332,115 @@
       <c r="C38" s="3" t="n"/>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1615
-</t>
+          <t>421</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3228
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">2515
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">213
+</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">492
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">941
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7857
-</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="n"/>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="n"/>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">410
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t xml:space="preserve">269
+</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">489
+          <t xml:space="preserve">12749
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2852
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -5753,47 +5466,47 @@
       <c r="C39" s="3" t="n"/>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">1326
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">546
+          <t xml:space="preserve">024516
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">1791
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
@@ -5805,32 +5518,31 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9
-</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="n"/>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="n"/>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -5841,37 +5553,36 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">19482
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">716
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
@@ -5889,135 +5600,130 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">422
-</t>
-        </is>
-      </c>
+      <c r="C40" s="3" t="n"/>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
+          <t xml:space="preserve">018
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">1890
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">941
+          <t xml:space="preserve">1910
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>421</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="O40" s="3" t="n"/>
+          <t xml:space="preserve">1070
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="n"/>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">923
+</t>
+        </is>
+      </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">2998
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t xml:space="preserve">270
+</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">398
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2478
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">869
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -6035,135 +5741,125 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">422
-</t>
-        </is>
-      </c>
+      <c r="C41" s="3" t="n"/>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
+          <t xml:space="preserve">2324
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">10856
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="n"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">10820
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">869
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -6190,133 +5886,121 @@
       <c r="C42" s="3" t="n"/>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">11229
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">11020
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">544
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">1628
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">941
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="n"/>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">931
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">2662
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="n"/>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">2492
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">963
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">12221
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">9603
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5822
+          <t xml:space="preserve">102712
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">2167
 </t>
         </is>
       </c>
@@ -6335,134 +6019,28 @@
         </is>
       </c>
       <c r="C43" s="3" t="n"/>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">324
-</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1285
-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1142
-745
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225778
-22
-</t>
-        </is>
-      </c>
+      <c r="D43" s="3" t="n"/>
+      <c r="E43" s="3" t="n"/>
+      <c r="F43" s="3" t="n"/>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+      <c r="I43" s="3" t="n"/>
+      <c r="J43" s="3" t="n"/>
+      <c r="K43" s="3" t="n"/>
+      <c r="L43" s="3" t="n"/>
+      <c r="M43" s="3" t="n"/>
+      <c r="N43" s="3" t="n"/>
       <c r="O43" s="3" t="n"/>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-6
-</t>
-        </is>
-      </c>
-      <c r="T43" s="3" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">953
-</t>
-        </is>
-      </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">852
-</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
+      <c r="P43" s="3" t="n"/>
+      <c r="Q43" s="3" t="n"/>
+      <c r="R43" s="3" t="n"/>
+      <c r="S43" s="3" t="n"/>
+      <c r="T43" s="3" t="n"/>
+      <c r="U43" s="3" t="n"/>
+      <c r="V43" s="3" t="n"/>
+      <c r="W43" s="3" t="n"/>
+      <c r="X43" s="3" t="n"/>
+      <c r="Y43" s="3" t="n"/>
       <c r="Z43" s="3" t="n"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -6478,118 +6056,28 @@
         </is>
       </c>
       <c r="C44" s="3" t="n"/>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4262
-7
-</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">442
-</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2429
-14
-</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77
-</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-7
-</t>
-        </is>
-      </c>
+      <c r="D44" s="3" t="n"/>
+      <c r="E44" s="3" t="n"/>
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+      <c r="I44" s="3" t="n"/>
+      <c r="J44" s="3" t="n"/>
+      <c r="K44" s="3" t="n"/>
       <c r="L44" s="3" t="n"/>
       <c r="M44" s="3" t="n"/>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77 777
-</t>
-        </is>
-      </c>
+      <c r="N44" s="3" t="n"/>
       <c r="O44" s="3" t="n"/>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">828
-</t>
-        </is>
-      </c>
-      <c r="S44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2418
-</t>
-        </is>
-      </c>
+      <c r="P44" s="3" t="n"/>
+      <c r="Q44" s="3" t="n"/>
+      <c r="R44" s="3" t="n"/>
+      <c r="S44" s="3" t="n"/>
       <c r="T44" s="3" t="n"/>
-      <c r="U44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="V44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="W44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
-      <c r="X44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3272
-</t>
-        </is>
-      </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t>504</t>
-        </is>
-      </c>
+      <c r="U44" s="3" t="n"/>
+      <c r="V44" s="3" t="n"/>
+      <c r="W44" s="3" t="n"/>
+      <c r="X44" s="3" t="n"/>
+      <c r="Y44" s="3" t="n"/>
       <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -6607,7 +6095,7 @@
       <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">323
 </t>
         </is>
       </c>
@@ -6619,99 +6107,107 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1929
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
+          <t xml:space="preserve">1175
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>455</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2828
-</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1909
+</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="n"/>
+      <c r="L45" s="3" t="n"/>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41272728
-1 8
-</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="n"/>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="Q45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="n"/>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="T45" s="3" t="n"/>
+          <t xml:space="preserve">1605
+</t>
+        </is>
+      </c>
+      <c r="T45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="V45" s="3" t="n"/>
-      <c r="W45" s="3" t="n"/>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
-</t>
-        </is>
-      </c>
-      <c r="Y45" s="3" t="n"/>
+          <t>821</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">518
+</t>
+        </is>
+      </c>
       <c r="Z45" s="3" t="n"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -6728,102 +6224,47 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 191
-</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">323
-</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n"/>
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="3" t="n"/>
       <c r="H46" s="3" t="n"/>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
+      <c r="I46" s="3" t="n"/>
+      <c r="J46" s="3" t="n"/>
       <c r="K46" s="3" t="n"/>
       <c r="L46" s="3" t="n"/>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-278
-</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">062
-</t>
-        </is>
-      </c>
+      <c r="M46" s="3" t="n"/>
+      <c r="N46" s="3" t="n"/>
+      <c r="O46" s="3" t="n"/>
+      <c r="P46" s="3" t="n"/>
       <c r="Q46" s="3" t="n"/>
       <c r="R46" s="3" t="n"/>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+      <c r="S46" s="3" t="n"/>
       <c r="T46" s="3" t="n"/>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12901
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1999
-</t>
-        </is>
-      </c>
+      <c r="U46" s="3" t="n"/>
+      <c r="V46" s="3" t="n"/>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">749
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="n"/>
-      <c r="Y46" s="3" t="n"/>
+          <t xml:space="preserve">92110
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198855
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1165608
+</t>
+        </is>
+      </c>
       <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/508/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/508/original_transcribed_data.xlsx
@@ -741,7 +741,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">845
 </t>
         </is>
       </c>
@@ -753,7 +753,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -763,10 +763,15 @@
 </t>
         </is>
       </c>
-      <c r="J4" s="3" t="n"/>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1829
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -778,19 +783,19 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
@@ -802,7 +807,8 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>326</t>
+          <t xml:space="preserve">306
+</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
@@ -813,13 +819,14 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>5452</t>
+          <t xml:space="preserve">452
+</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -859,13 +866,13 @@
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -877,19 +884,19 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -907,13 +914,13 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2176
+          <t xml:space="preserve">7146
 </t>
         </is>
       </c>
@@ -925,17 +932,19 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>314</t>
+          <t xml:space="preserve">994
+</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -947,7 +956,7 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -959,36 +968,38 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t xml:space="preserve">165
+</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1299
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t xml:space="preserve">68
+</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1007,25 +1018,25 @@
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">342
+          <t xml:space="preserve">382
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0170
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -1035,7 +1046,12 @@
 </t>
         </is>
       </c>
-      <c r="I6" s="3" t="n"/>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">44
@@ -1044,74 +1060,79 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">975
+</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">812
+</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">295
+</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">906
+</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">144
 </t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1175
-</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">812
-</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">295
-</t>
-        </is>
-      </c>
-      <c r="R6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2074
-</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1144
-</t>
-        </is>
-      </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2513
+          <t xml:space="preserve">413
 </t>
         </is>
       </c>
@@ -1129,7 +1150,7 @@
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -1149,7 +1170,7 @@
       <c r="C7" s="3" t="n"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2105
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
@@ -1161,7 +1182,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -1173,7 +1194,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1798
 </t>
         </is>
       </c>
@@ -1197,21 +1218,27 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1203
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="n"/>
-      <c r="O7" s="3" t="n"/>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">906
+</t>
+        </is>
+      </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>013</t>
+          <t xml:space="preserve">82
+</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1228,22 +1255,17 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
-</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">812
+</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="n"/>
       <c r="V7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">214
@@ -1258,7 +1280,7 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
@@ -1268,7 +1290,12 @@
 </t>
         </is>
       </c>
-      <c r="Z7" s="3" t="n"/>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -1291,13 +1318,13 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
@@ -1315,18 +1342,20 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">2
+</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t xml:space="preserve">14
+</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -1344,13 +1373,14 @@
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t xml:space="preserve">080
+</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1361,7 +1391,7 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -1373,7 +1403,8 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>662</t>
+          <t xml:space="preserve">662
+</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
@@ -1384,7 +1415,7 @@
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2946
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -1396,15 +1427,22 @@
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>236</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="n"/>
+          <t xml:space="preserve">592
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1427,43 +1465,43 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1125
+          <t xml:space="preserve">1185
 </t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">578
+          <t xml:space="preserve">518
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9578
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">096
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9492
+          <t xml:space="preserve">471
 </t>
         </is>
       </c>
@@ -1479,10 +1517,15 @@
 </t>
         </is>
       </c>
-      <c r="N9" s="3" t="n"/>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1001
+</t>
+        </is>
+      </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14546
+          <t xml:space="preserve">4516
 </t>
         </is>
       </c>
@@ -1500,13 +1543,14 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11109
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t xml:space="preserve">1260
+</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
@@ -1517,27 +1561,31 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19488
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">1298
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
-</t>
-        </is>
-      </c>
-      <c r="X9" s="3" t="n"/>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2311
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="Z9" s="3" t="n"/>
@@ -1563,23 +1611,28 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="n"/>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51
+</t>
+        </is>
+      </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">19
@@ -1588,7 +1641,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">972
+          <t xml:space="preserve">08604
 </t>
         </is>
       </c>
@@ -1601,10 +1654,16 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>814</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="n"/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">912
@@ -1613,8 +1672,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -1637,13 +1695,13 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1642
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1655,25 +1713,25 @@
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12822
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2162
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -1699,38 +1757,44 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">1105
 </t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="n"/>
+          <t xml:space="preserve">2128
+</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>483</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -1741,16 +1805,22 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t xml:space="preserve">1183
+</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="n"/>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -1759,54 +1829,55 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">284
+</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">2398
 </t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
+          <t xml:space="preserve">2657
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1612
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
@@ -1824,7 +1895,12 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">264
@@ -1833,7 +1909,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1183
 </t>
         </is>
       </c>
@@ -1845,13 +1921,13 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
@@ -1863,76 +1939,88 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05
+</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1226
+</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">902
+</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">672
+</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">218
 </t>
         </is>
       </c>
-      <c r="K12" s="3" t="n"/>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="n"/>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">902
-</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="R12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="S12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1612
-</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="W12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">244
@@ -1941,11 +2029,16 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1945
-</t>
-        </is>
-      </c>
-      <c r="Z12" s="3" t="n"/>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1645
+</t>
+        </is>
+      </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -1968,45 +2061,61 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">89
+</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="n"/>
-      <c r="K13" s="3" t="n"/>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">275
+</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -2018,19 +2127,20 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>464</t>
+          <t xml:space="preserve">204
+</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -2047,7 +2157,7 @@
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -2065,17 +2175,22 @@
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1852
-</t>
-        </is>
-      </c>
-      <c r="Z13" s="3" t="n"/>
+          <t xml:space="preserve">852
+</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -2089,7 +2204,12 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 3 3 1
+</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">299
@@ -2104,13 +2224,13 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1495
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -2134,54 +2254,61 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>43414</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="n"/>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">814
+</t>
+        </is>
+      </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">04
+</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29234
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">582
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -2193,7 +2320,7 @@
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
+          <t xml:space="preserve">2151
 </t>
         </is>
       </c>
@@ -2211,11 +2338,16 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">514
-</t>
-        </is>
-      </c>
-      <c r="Z14" s="3" t="n"/>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9514
+</t>
+        </is>
+      </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>9</t>
@@ -2232,19 +2364,20 @@
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">28919
 </t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">295
+</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -2255,20 +2388,26 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="n"/>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>08</t>
+          <t xml:space="preserve">114
+</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -2279,26 +2418,31 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="n"/>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">919
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">014
 </t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -2310,47 +2454,52 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">048
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">382
+          <t xml:space="preserve">582
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">2095
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">853
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="Z15" s="3" t="n"/>
+          <t xml:space="preserve">85
+</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>10</t>
@@ -2385,12 +2534,13 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">481
+</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -2402,14 +2552,20 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="n"/>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+</t>
+        </is>
+      </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">9513
+</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -2420,29 +2576,31 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t xml:space="preserve">94552
+</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">114
+</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11823
+          <t xml:space="preserve">11829
 </t>
         </is>
       </c>
@@ -2454,37 +2612,32 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">213142
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19492
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">11585
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11246
-</t>
-        </is>
-      </c>
-      <c r="X16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17088
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">112746
+</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="n"/>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11510
+          <t xml:space="preserve">1005
 </t>
         </is>
       </c>
@@ -2502,22 +2655,27 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1895
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -2529,58 +2687,68 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4129
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="n"/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="n"/>
+          <t xml:space="preserve">1187
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1912
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">2518
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
@@ -2598,14 +2766,19 @@
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">222 3
+</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">215
 </t>
         </is>
       </c>
-      <c r="W17" s="3" t="n"/>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -2632,12 +2805,13 @@
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>302</t>
+          <t xml:space="preserve">3089
+</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -2655,18 +2829,19 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>466</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -2678,33 +2853,39 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4110
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="n"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2288
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1072
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="n"/>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">232
+</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -2715,31 +2896,31 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">548
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -2766,7 +2947,7 @@
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29505
+          <t xml:space="preserve">1097
 </t>
         </is>
       </c>
@@ -2790,34 +2971,50 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="n"/>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="n"/>
+          <t xml:space="preserve">14183
+</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
       <c r="N19" s="3" t="n"/>
-      <c r="O19" s="3" t="n"/>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">02
+</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -2828,49 +3025,49 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="T19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">230
 </t>
         </is>
       </c>
-      <c r="T19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="V19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="W19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="X19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1218
-</t>
-        </is>
-      </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -2888,10 +3085,16 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">2853
+</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -2908,13 +3111,14 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>486</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -2925,33 +3129,44 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="n"/>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="N20" s="3" t="n"/>
-      <c r="O20" s="3" t="n"/>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">902
+</t>
+        </is>
+      </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -2969,36 +3184,37 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t xml:space="preserve">109
+</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -3019,7 +3235,7 @@
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -3031,19 +3247,19 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1013
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -3061,26 +3277,32 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">738
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">184
 </t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
       <c r="N21" s="3" t="n"/>
-      <c r="O21" s="3" t="n"/>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -3092,7 +3314,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -3104,19 +3326,19 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -3126,15 +3348,10 @@
 </t>
         </is>
       </c>
-      <c r="X21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">902
-</t>
-        </is>
-      </c>
+      <c r="X21" s="3" t="n"/>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -3155,19 +3372,19 @@
       <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -3179,19 +3396,19 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -3203,26 +3420,31 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="n"/>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1108
+</t>
+        </is>
+      </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -3234,7 +3456,7 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -3246,28 +3468,28 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9562
+          <t xml:space="preserve">8562
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1399
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">226
 </t>
         </is>
       </c>
-      <c r="W22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">802
@@ -3276,7 +3498,7 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1947
+          <t xml:space="preserve">947
 </t>
         </is>
       </c>
@@ -3294,33 +3516,48 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11441
+          <t xml:space="preserve">19446
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2904
+          <t xml:space="preserve">9104
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
-</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="n"/>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">572
+</t>
+        </is>
+      </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="n"/>
+          <t xml:space="preserve">2208
+</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">725
+</t>
+        </is>
+      </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">140
@@ -3329,25 +3566,26 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">024644
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>71</t>
+          <t xml:space="preserve">939
+</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14209
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="n"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9316
+          <t xml:space="preserve">9312
 </t>
         </is>
       </c>
@@ -3359,7 +3597,7 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11210
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
@@ -3371,36 +3609,37 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">112
+</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93606
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11084
+          <t xml:space="preserve">479
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1026
+          <t xml:space="preserve">1086
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1977
+          <t xml:space="preserve">1974
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09278
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
@@ -3427,25 +3666,25 @@
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">2825
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18298
+          <t xml:space="preserve">8228
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">1914
 </t>
         </is>
       </c>
@@ -3457,11 +3696,16 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="n"/>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10589
+</t>
+        </is>
+      </c>
       <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
@@ -3471,14 +3715,20 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>13164</t>
+          <t xml:space="preserve">2186
+</t>
         </is>
       </c>
       <c r="N24" s="3" t="n"/>
-      <c r="O24" s="3" t="n"/>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 312
+</t>
+        </is>
+      </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -3490,19 +3740,19 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7282
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -3514,22 +3764,17 @@
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2817
+</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">205
 </t>
         </is>
       </c>
-      <c r="W24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
-      <c r="X24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">852
-</t>
-        </is>
-      </c>
+      <c r="X24" s="3" t="n"/>
       <c r="Y24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">25
@@ -3559,7 +3804,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3577,13 +3822,13 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -3595,7 +3840,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -3607,20 +3852,20 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="n"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11922
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1090
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -3632,7 +3877,8 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>430</t>
+          <t xml:space="preserve">230
+</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -3643,37 +3889,37 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">859
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1692
+          <t xml:space="preserve">1678
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">591
 </t>
         </is>
       </c>
@@ -3694,13 +3940,13 @@
       <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1592
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -3724,7 +3970,8 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">12
+</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -3735,27 +3982,37 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="n"/>
-      <c r="N26" s="3" t="n"/>
+          <t xml:space="preserve">1926
+</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7 18
+</t>
+        </is>
+      </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
+          <t xml:space="preserve">7 91
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -3767,19 +4024,18 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">479
 </t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7162
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -3803,7 +4059,7 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1862
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
@@ -3827,7 +4083,12 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">273
@@ -3836,7 +4097,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1974
+          <t xml:space="preserve">974
 </t>
         </is>
       </c>
@@ -3854,7 +4115,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -3872,7 +4133,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -3884,14 +4145,20 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="n"/>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1111
+</t>
+        </is>
+      </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>494</t>
+          <t xml:space="preserve">48
+</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -3908,7 +4175,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -3920,32 +4187,32 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">632
+</t>
+        </is>
+      </c>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">109
 </t>
         </is>
       </c>
-      <c r="U27" s="3" t="n"/>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
-</t>
-        </is>
-      </c>
-      <c r="W27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1214
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="n"/>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1802
+          <t xml:space="preserve">802
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -3966,13 +4233,13 @@
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1079
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -3984,19 +4251,19 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -4008,31 +4275,37 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>463</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1687
-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="n"/>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190809
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
@@ -4044,13 +4317,14 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>256</t>
+          <t xml:space="preserve">2740
+</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
@@ -4061,31 +4335,31 @@
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5622
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">538
+          <t xml:space="preserve">532
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -4112,68 +4386,72 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05
+</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">112
 </t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1918
-</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">05
-</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1892
-</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1958
-</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="n"/>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>403</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -4203,31 +4481,31 @@
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1394
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1862
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4245,10 +4523,15 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194984
+          <t xml:space="preserve">19484
 </t>
         </is>
       </c>
@@ -4278,92 +4561,98 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2927
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="n"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>412</t>
+          <t xml:space="preserve">451
+</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
+          <t xml:space="preserve">9207
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11123
-</t>
-        </is>
-      </c>
-      <c r="S30" s="3" t="n"/>
+          <t xml:space="preserve">1129
+</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1264
+</t>
+        </is>
+      </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1538222
+          <t xml:space="preserve">33222
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">10881
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11042
+          <t xml:space="preserve">11841
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">1156
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3126
+          <t xml:space="preserve">1084
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9284
+          <t xml:space="preserve">954
 </t>
         </is>
       </c>
@@ -4384,13 +4673,13 @@
       <c r="C31" s="3" t="n"/>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">2397
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -4402,7 +4691,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -4414,23 +4703,35 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">21
+</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="n"/>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>485</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="n"/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">912
@@ -4439,61 +4740,61 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1826
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
+          <t xml:space="preserve">649
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">773
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -4514,30 +4815,32 @@
       <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14183
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>86</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">1118
+</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -4548,7 +4851,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4570,10 +4873,15 @@
 </t>
         </is>
       </c>
-      <c r="N32" s="3" t="n"/>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12196
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
@@ -4591,7 +4899,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -4603,31 +4911,31 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">2881
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">4155
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
+          <t xml:space="preserve">842
 </t>
         </is>
       </c>
@@ -4646,7 +4954,12 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n"/>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+</t>
+        </is>
+      </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">326
@@ -4655,19 +4968,19 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -4679,33 +4992,43 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">945
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="n"/>
-      <c r="N33" s="3" t="n"/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1109
+</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">598
 </t>
         </is>
       </c>
@@ -4735,37 +5058,37 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">486
+</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">150
 </t>
         </is>
       </c>
-      <c r="U33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1803
+          <t xml:space="preserve">803
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1688
+          <t xml:space="preserve">1658
 </t>
         </is>
       </c>
@@ -4783,10 +5106,15 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n"/>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
@@ -4798,7 +5126,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2418
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -4816,19 +5144,19 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">935
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -4838,18 +5166,33 @@
 </t>
         </is>
       </c>
-      <c r="M34" s="3" t="n"/>
-      <c r="N34" s="3" t="n"/>
-      <c r="O34" s="3" t="n"/>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1511
+</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12825
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -4867,13 +5210,14 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">682
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">90
+</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
@@ -4884,19 +5228,19 @@
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1863
+          <t xml:space="preserve">863
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -4917,31 +5261,30 @@
       <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">004
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -4969,11 +5312,21 @@
 </t>
         </is>
       </c>
-      <c r="M35" s="3" t="n"/>
-      <c r="N35" s="3" t="n"/>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">301
+</t>
+        </is>
+      </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">9942
 </t>
         </is>
       </c>
@@ -5003,19 +5356,19 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2517
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8320
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -5027,13 +5380,13 @@
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1628
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
@@ -5054,7 +5407,7 @@
       <c r="C36" s="3" t="n"/>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">336
 </t>
         </is>
       </c>
@@ -5078,19 +5431,19 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1514
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">590
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -5107,28 +5460,33 @@
         </is>
       </c>
       <c r="M36" s="3" t="n"/>
-      <c r="N36" s="3" t="n"/>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">4706
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12312
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -5146,7 +5504,7 @@
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -5164,13 +5522,13 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3852
+          <t xml:space="preserve">557
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -5197,7 +5555,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
@@ -5209,46 +5567,52 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0694
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87110
+          <t xml:space="preserve">8180
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">0117
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>203</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">422
+          <t xml:space="preserve">499
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9811
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9410
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="n"/>
+          <t xml:space="preserve">7210
+</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">9506
@@ -5257,7 +5621,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1206
 </t>
         </is>
       </c>
@@ -5269,34 +5633,34 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1170
+</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1206
+</t>
+        </is>
+      </c>
+      <c r="T37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1010
+</t>
+        </is>
+      </c>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1241
+</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1110
 </t>
         </is>
       </c>
-      <c r="S37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2413
-</t>
-        </is>
-      </c>
-      <c r="T37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1009
-</t>
-        </is>
-      </c>
-      <c r="U37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1248
-</t>
-        </is>
-      </c>
-      <c r="V37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1160
-</t>
-        </is>
-      </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1299
@@ -5305,13 +5669,13 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3672
+          <t xml:space="preserve">36722
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">372
+          <t xml:space="preserve">5372
 </t>
         </is>
       </c>
@@ -5332,7 +5696,8 @@
       <c r="C38" s="3" t="n"/>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>421</t>
+          <t xml:space="preserve">123
+</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -5343,7 +5708,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2515
+          <t xml:space="preserve">25246
 </t>
         </is>
       </c>
@@ -5355,44 +5720,50 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">941
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">144
+</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="n"/>
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
+          <t xml:space="preserve">507
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5410,25 +5781,25 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12749
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
@@ -5446,7 +5817,8 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="Z38" s="3" t="n"/>
@@ -5466,72 +5838,75 @@
       <c r="C39" s="3" t="n"/>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1326
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">024516
+          <t xml:space="preserve">856
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1791
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">11
+</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">29
+</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">682
 </t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1810
 </t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">1130
 </t>
         </is>
       </c>
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">786
 </t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>00</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -5542,7 +5917,8 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>226</t>
+          <t xml:space="preserve">1426
+</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -5553,13 +5929,14 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19482
+          <t xml:space="preserve">616
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t>286</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
@@ -5576,16 +5953,11 @@
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="Y39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1144
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="n"/>
       <c r="Z39" s="3" t="n"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -5603,67 +5975,73 @@
       <c r="C40" s="3" t="n"/>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">018
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">854
 </t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1910
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>421</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1070
-</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="n"/>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5118
+</t>
+        </is>
+      </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
@@ -5675,31 +6053,31 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2998
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">2608
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
+          <t xml:space="preserve">1926
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -5711,13 +6089,13 @@
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">2518
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">869
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -5744,19 +6122,19 @@
       <c r="C41" s="3" t="n"/>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2324
+          <t xml:space="preserve">9218
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10856
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -5768,44 +6146,44 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">2049
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="n"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
@@ -5817,25 +6195,25 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10820
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -5853,13 +6231,13 @@
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -5886,124 +6264,111 @@
       <c r="C42" s="3" t="n"/>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11229
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11020
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">544
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1628
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="n"/>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">19502
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2662
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="n"/>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2492
-</t>
-        </is>
-      </c>
-      <c r="T42" s="3" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1265
+</t>
+        </is>
+      </c>
+      <c r="T42" s="3" t="n"/>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">963
-</t>
-        </is>
-      </c>
-      <c r="V42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12221
-</t>
-        </is>
-      </c>
-      <c r="W42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9603
-</t>
-        </is>
-      </c>
-      <c r="X42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102712
-</t>
-        </is>
-      </c>
-      <c r="Y42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2167
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1010
+</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="n"/>
+      <c r="W42" s="3" t="n"/>
+      <c r="X42" s="3" t="n"/>
+      <c r="Y42" s="3" t="n"/>
       <c r="Z42" s="3" t="n"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -6018,7 +6383,12 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="n"/>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D43" s="3" t="n"/>
       <c r="E43" s="3" t="n"/>
       <c r="F43" s="3" t="n"/>
@@ -6055,7 +6425,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n"/>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D44" s="3" t="n"/>
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="n"/>
@@ -6095,116 +6470,128 @@
       <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1175
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">99
+</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1909
-</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="n"/>
-      <c r="L45" s="3" t="n"/>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">2666
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="n"/>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605
+          <t xml:space="preserve">2412
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">5097
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">962
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">8187
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">9663
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>821</t>
+          <t xml:space="preserve">02712
+</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">518
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -6222,46 +6609,121 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="n"/>
-      <c r="E46" s="3" t="n"/>
-      <c r="F46" s="3" t="n"/>
-      <c r="G46" s="3" t="n"/>
-      <c r="H46" s="3" t="n"/>
-      <c r="I46" s="3" t="n"/>
-      <c r="J46" s="3" t="n"/>
+      <c r="C46" s="3" t="n"/>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">937
+</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
       <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="n"/>
-      <c r="M46" s="3" t="n"/>
-      <c r="N46" s="3" t="n"/>
-      <c r="O46" s="3" t="n"/>
-      <c r="P46" s="3" t="n"/>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
       <c r="Q46" s="3" t="n"/>
-      <c r="R46" s="3" t="n"/>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
       <c r="S46" s="3" t="n"/>
-      <c r="T46" s="3" t="n"/>
-      <c r="U46" s="3" t="n"/>
-      <c r="V46" s="3" t="n"/>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">602
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92110
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198855
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165608
+          <t xml:space="preserve">12111011
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/508/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/508/original_transcribed_data.xlsx
@@ -729,7 +729,7 @@
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
@@ -741,7 +741,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -753,7 +753,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
@@ -789,13 +789,12 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
@@ -819,14 +818,13 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">452
-</t>
+          <t>452</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -837,7 +835,7 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -863,7 +861,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">252
@@ -878,7 +881,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -890,25 +893,24 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -920,19 +922,19 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7146
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">994
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
@@ -956,7 +958,7 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
@@ -968,19 +970,19 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">2439
 </t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
@@ -1018,121 +1020,121 @@
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">382
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">070
 </t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">276
+</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">944
+</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">295
+</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">272
 </t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">975
-</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">812
-</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">295
-</t>
-        </is>
-      </c>
-      <c r="R6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">906
-</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">413
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
@@ -1144,7 +1146,7 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">772
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -1237,13 +1239,13 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">4201
 </t>
         </is>
       </c>
@@ -1255,17 +1257,22 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="n"/>
+          <t xml:space="preserve">872
+</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">214
@@ -1280,7 +1287,7 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -1292,7 +1299,7 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -1309,7 +1316,12 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">268
@@ -1324,7 +1336,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -1342,13 +1354,13 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1403,7 +1415,7 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -1415,7 +1427,7 @@
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -1433,13 +1445,13 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
+          <t xml:space="preserve">692
 </t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -1465,7 +1477,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">896
 </t>
         </is>
       </c>
@@ -1477,7 +1489,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">518
+          <t xml:space="preserve">548
 </t>
         </is>
       </c>
@@ -1495,28 +1507,28 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">471
+          <t xml:space="preserve">9441
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">928
+</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">926
 </t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">926
-</t>
-        </is>
-      </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1001
@@ -1525,8 +1537,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4516
-</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1549,7 +1560,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
@@ -1561,13 +1572,13 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">488
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1298
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
@@ -1585,7 +1596,8 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>314</t>
+          <t xml:space="preserve">311
+</t>
         </is>
       </c>
       <c r="Z9" s="3" t="n"/>
@@ -1602,7 +1614,12 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 1
+</t>
+        </is>
+      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">295
@@ -1623,13 +1640,13 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1916
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -1641,11 +1658,16 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08604
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n"/>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">185
@@ -1660,7 +1682,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -1701,7 +1723,7 @@
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -1731,7 +1753,7 @@
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -1775,13 +1797,13 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
@@ -1793,14 +1815,13 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1811,16 +1832,11 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="n"/>
       <c r="P11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -1835,31 +1851,31 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2398
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2657
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -1871,7 +1887,7 @@
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -1897,7 +1913,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
@@ -1909,7 +1925,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -1921,13 +1937,13 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -1945,7 +1961,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">046
 </t>
         </is>
       </c>
@@ -1963,7 +1979,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -1981,7 +1997,7 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -1993,19 +2009,19 @@
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">672
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -2017,7 +2033,7 @@
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -2029,13 +2045,13 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1645
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -2067,7 +2083,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -2079,7 +2095,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -2091,7 +2107,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -2115,7 +2131,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -2133,7 +2149,7 @@
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -2157,7 +2173,7 @@
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -2204,12 +2220,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 3 3 1
-</t>
-        </is>
-      </c>
+      <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">299
@@ -2224,7 +2235,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -2236,7 +2247,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -2266,19 +2277,14 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">814
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="n"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
@@ -2290,7 +2296,7 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -2302,13 +2308,13 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
@@ -2320,7 +2326,7 @@
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2151
+          <t xml:space="preserve">1151
 </t>
         </is>
       </c>
@@ -2338,13 +2344,13 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">7172
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9514
+          <t xml:space="preserve">514
 </t>
         </is>
       </c>
@@ -2361,16 +2367,21 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28919
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -2394,19 +2405,19 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2418,25 +2429,25 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
+          <t xml:space="preserve">915
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">014
+          <t xml:space="preserve">012
 </t>
         </is>
       </c>
@@ -2454,7 +2465,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">048
+          <t xml:space="preserve">1227
 </t>
         </is>
       </c>
@@ -2478,7 +2489,7 @@
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2095
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -2496,7 +2507,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -2516,19 +2527,18 @@
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1408
+          <t xml:space="preserve">19404
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
-</t>
+          <t>443</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
@@ -2540,7 +2550,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">015
 </t>
         </is>
       </c>
@@ -2552,13 +2562,13 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -2582,7 +2592,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94552
+          <t xml:space="preserve">4532
 </t>
         </is>
       </c>
@@ -2594,13 +2604,13 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11829
+          <t xml:space="preserve">11273
 </t>
         </is>
       </c>
@@ -2612,32 +2622,32 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213142
+          <t xml:space="preserve">0182
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11585
+          <t xml:space="preserve">9848
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112746
+          <t xml:space="preserve">11246
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="n"/>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1005
+          <t xml:space="preserve">100646
 </t>
         </is>
       </c>
@@ -2655,15 +2665,10 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
-      </c>
+      <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
@@ -2675,7 +2680,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
@@ -2699,7 +2704,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -2712,16 +2717,11 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="n"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">91
@@ -2730,7 +2730,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -2742,19 +2742,19 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">2353
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">649
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222 3
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -2805,37 +2805,36 @@
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3089
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -2853,13 +2852,13 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -2878,8 +2877,7 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
@@ -2896,13 +2894,13 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
+          <t xml:space="preserve">942
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -2914,7 +2912,7 @@
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -2944,10 +2942,15 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1097
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
@@ -2971,7 +2974,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>469</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -2994,7 +2997,7 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14183
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -3031,19 +3034,19 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -3085,21 +3088,16 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
+      <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2853
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -3147,11 +3145,16 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="n"/>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">902
@@ -3178,25 +3181,25 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">722
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
@@ -3208,7 +3211,7 @@
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -3235,8 +3238,7 @@
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3253,22 +3255,22 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">10
 </t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">19
@@ -3277,7 +3279,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">738
 </t>
         </is>
       </c>
@@ -3308,13 +3310,13 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -3326,13 +3328,13 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">883
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
@@ -3372,8 +3374,7 @@
       <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>374</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -3384,34 +3385,34 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2328
+</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">232
 </t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -3426,13 +3427,13 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -3468,7 +3469,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8562
+          <t xml:space="preserve">89562
 </t>
         </is>
       </c>
@@ -3516,58 +3517,51 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
+      <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19446
+          <t xml:space="preserve">1944
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9104
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2208
+          <t xml:space="preserve">858
 </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -3578,23 +3572,22 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="n"/>
+          <t xml:space="preserve">929
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9312
-</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="n"/>
       <c r="Q23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1210
@@ -3603,7 +3596,7 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1072
+          <t xml:space="preserve">1079
 </t>
         </is>
       </c>
@@ -3615,7 +3608,7 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">3602
 </t>
         </is>
       </c>
@@ -3633,19 +3626,19 @@
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1974
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">0949278
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -3666,7 +3659,7 @@
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2825
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
@@ -3678,13 +3671,13 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8228
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1914
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -3696,20 +3689,19 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10589
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
@@ -3722,13 +3714,13 @@
       <c r="N24" s="3" t="n"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 312
+          <t xml:space="preserve">5812
 </t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -3740,19 +3732,19 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">28239
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">782
 </t>
         </is>
       </c>
@@ -3764,7 +3756,7 @@
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2817
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -3795,11 +3787,15 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -3810,56 +3806,50 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n"/>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="n"/>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="n"/>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -3889,8 +3879,7 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
@@ -3901,25 +3890,25 @@
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1678
+          <t xml:space="preserve">8713
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">591
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -3940,7 +3929,7 @@
       <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">2986
 </t>
         </is>
       </c>
@@ -3964,7 +3953,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -3982,37 +3971,32 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1926
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7 18
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="n"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7 91
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4024,18 +4008,19 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">479
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">762
 </t>
         </is>
       </c>
@@ -4083,12 +4068,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+      <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">273
@@ -4097,7 +4077,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">974
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -4115,7 +4095,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -4127,13 +4107,13 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -4145,19 +4125,19 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">8118
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -4169,13 +4149,13 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -4193,13 +4173,13 @@
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -4212,7 +4192,7 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -4233,13 +4213,13 @@
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -4251,7 +4231,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -4263,7 +4243,7 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -4275,37 +4255,36 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">12724
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -4323,7 +4302,7 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2740
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
@@ -4335,32 +4314,31 @@
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">2228
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">532
+          <t xml:space="preserve">534
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>856</t>
         </is>
       </c>
       <c r="Z28" s="3" t="n"/>
@@ -4398,7 +4376,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -4410,7 +4388,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4434,19 +4412,14 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="n"/>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>407</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
@@ -4469,7 +4442,7 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
@@ -4493,7 +4466,7 @@
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -4505,7 +4478,7 @@
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -4523,27 +4496,22 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
+      <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19484
+          <t xml:space="preserve">1494
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
@@ -4573,44 +4541,43 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">961
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="n"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">451
-</t>
+          <t>453</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9207
+          <t xml:space="preserve">1307
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">1127
 </t>
         </is>
       </c>
@@ -4622,37 +4589,36 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33222
+          <t xml:space="preserve">3222
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10881
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11841
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1084
-</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">954
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
@@ -4673,19 +4639,19 @@
       <c r="C31" s="3" t="n"/>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2397
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -4716,7 +4682,7 @@
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
@@ -4728,7 +4694,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -4740,7 +4706,7 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4752,7 +4718,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
@@ -4764,13 +4730,13 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">649
+          <t xml:space="preserve">641
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -4794,7 +4760,7 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
@@ -4815,8 +4781,7 @@
       <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>348</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -4827,7 +4792,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
@@ -4839,19 +4804,19 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -4863,25 +4828,20 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
+      <c r="N32" s="3" t="n"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
@@ -4899,7 +4859,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -4911,13 +4871,13 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2881
+          <t xml:space="preserve">352
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4155
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -4935,7 +4895,7 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">842
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -4954,21 +4914,15 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
-      </c>
+      <c r="C33" s="3" t="n"/>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -4992,7 +4946,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -5010,28 +4964,23 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">9198
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
-</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="n"/>
+      <c r="O33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">108
 </t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">598
-</t>
-        </is>
-      </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -5046,7 +4995,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -5058,7 +5007,7 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">486
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -5070,13 +5019,13 @@
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -5088,7 +5037,7 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1658
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -5106,12 +5055,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
+      <c r="C34" s="3" t="n"/>
       <c r="D34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">321
@@ -5120,7 +5064,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -5150,13 +5094,13 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -5168,19 +5112,19 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">1919
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1511
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -5192,7 +5136,7 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -5210,13 +5154,13 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">682
+          <t xml:space="preserve">692
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -5240,7 +5184,7 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
@@ -5261,19 +5205,20 @@
       <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">004
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">274
+</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -5284,7 +5229,7 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -5308,25 +5253,25 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9942
+          <t xml:space="preserve">1724
 </t>
         </is>
       </c>
@@ -5356,7 +5301,7 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1922
 </t>
         </is>
       </c>
@@ -5368,7 +5313,7 @@
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">320
 </t>
         </is>
       </c>
@@ -5386,7 +5331,7 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -5407,14 +5352,13 @@
       <c r="C36" s="3" t="n"/>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">336
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -5425,7 +5369,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -5437,13 +5381,13 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -5459,25 +5403,24 @@
 </t>
         </is>
       </c>
-      <c r="M36" s="3" t="n"/>
-      <c r="N36" s="3" t="inlineStr">
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1212
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="n"/>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">10
 </t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4706
-</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">312
@@ -5486,7 +5429,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -5498,7 +5441,7 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -5522,13 +5465,13 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">557
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -5549,13 +5492,13 @@
       <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11615
+          <t xml:space="preserve">1615
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
@@ -5567,61 +5510,61 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
+          <t xml:space="preserve">0694
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8180
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0117
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">499
+          <t xml:space="preserve">9499
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">981
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7210
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9506
+          <t xml:space="preserve">9502
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -5633,13 +5576,13 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
+          <t xml:space="preserve">12304
 </t>
         </is>
       </c>
@@ -5651,13 +5594,13 @@
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
@@ -5669,13 +5612,13 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36722
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372
+          <t xml:space="preserve">372
 </t>
         </is>
       </c>
@@ -5708,19 +5651,19 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25246
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -5732,32 +5675,31 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>468</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">507
+          <t xml:space="preserve">302
 </t>
         </is>
       </c>
@@ -5781,7 +5723,7 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -5799,7 +5741,7 @@
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -5817,7 +5759,7 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
@@ -5844,31 +5786,31 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -5880,26 +5822,26 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">682
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">786
+          <t xml:space="preserve">7960
 </t>
         </is>
       </c>
@@ -5917,7 +5859,7 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1426
+          <t xml:space="preserve">426
 </t>
         </is>
       </c>
@@ -5929,19 +5871,19 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">616
+          <t xml:space="preserve">692
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -5953,7 +5895,7 @@
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -5987,7 +5929,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -5999,7 +5941,7 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -6011,13 +5953,13 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
@@ -6035,7 +5977,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5118
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -6053,25 +5995,25 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">2312
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">2822
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2608
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1926
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -6089,13 +6031,13 @@
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2518
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -6122,34 +6064,34 @@
       <c r="C41" s="3" t="n"/>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9218
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">179 0
+</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">29
@@ -6158,7 +6100,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -6170,29 +6112,24 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2049
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="n"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">992
+</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="n"/>
       <c r="Q41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">24
@@ -6213,7 +6150,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -6225,8 +6162,7 @@
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
@@ -6237,7 +6173,7 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">682
 </t>
         </is>
       </c>
@@ -6270,25 +6206,25 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -6300,7 +6236,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -6312,22 +6248,17 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1984
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19502
-</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="n"/>
       <c r="O42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">922
@@ -6354,14 +6285,19 @@
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
-</t>
-        </is>
-      </c>
-      <c r="T42" s="3" t="n"/>
+          <t xml:space="preserve">276
+</t>
+        </is>
+      </c>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 14
+</t>
+        </is>
+      </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -6482,13 +6418,13 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">1620
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -6500,25 +6436,23 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>056</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">1411
 </t>
         </is>
       </c>
@@ -6530,13 +6464,12 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2666
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
@@ -6561,37 +6494,37 @@
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5097
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
+          <t xml:space="preserve">952
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8187
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9663
+          <t xml:space="preserve">963
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02712
+          <t xml:space="preserve">2212
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -6630,7 +6563,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">937
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -6648,20 +6581,25 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n"/>
+          <t xml:space="preserve">1041
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1427
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -6673,7 +6611,7 @@
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">923
 </t>
         </is>
       </c>
@@ -6717,13 +6655,13 @@
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">823
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12111011
+          <t xml:space="preserve">872085
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/508/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/508/original_transcribed_data.xlsx
@@ -729,7 +729,7 @@
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">397
 </t>
         </is>
       </c>
@@ -789,12 +789,13 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">288
+</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
@@ -818,13 +819,14 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>452</t>
+          <t xml:space="preserve">45
+</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -835,7 +837,7 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -861,15 +863,10 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
+      <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -881,19 +878,19 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -905,33 +902,34 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">20
 </t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">912
@@ -964,19 +962,19 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">702
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2439
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
@@ -994,7 +992,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
@@ -1026,13 +1024,13 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">070
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">1276
 </t>
         </is>
       </c>
@@ -1056,7 +1054,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">944
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
@@ -1080,19 +1078,19 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">9212
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -1116,13 +1114,13 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">3906
 </t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -1134,7 +1132,7 @@
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -1146,7 +1144,7 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -1172,7 +1170,7 @@
       <c r="C7" s="3" t="n"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">2305
 </t>
         </is>
       </c>
@@ -1184,7 +1182,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -1196,7 +1194,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1798
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -1214,7 +1212,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -1226,14 +1224,18 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="n"/>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
@@ -1245,7 +1247,7 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4201
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -1263,7 +1265,7 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
@@ -1287,19 +1289,19 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">742
+</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">862
-</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -1316,12 +1318,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+      <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">268
@@ -1336,8 +1333,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>426</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1354,7 +1350,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -1385,13 +1381,13 @@
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">7912
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1415,7 +1411,7 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">662
 </t>
         </is>
       </c>
@@ -1427,7 +1423,7 @@
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -1445,13 +1441,13 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
@@ -1471,14 +1467,13 @@
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1474
+          <t xml:space="preserve">1479
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
-</t>
+          <t>836</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1489,14 +1484,13 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
+          <t xml:space="preserve">578
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1507,37 +1501,38 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9441
+          <t xml:space="preserve">441
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">39726
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1001
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>4525</t>
+          <t xml:space="preserve">4512
+</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1554,13 +1549,13 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
@@ -1590,17 +1585,21 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">3826
+</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">311
 </t>
         </is>
       </c>
-      <c r="Z9" s="3" t="n"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1614,12 +1613,7 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 1
-</t>
-        </is>
-      </c>
+      <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">295
@@ -1628,7 +1622,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -1640,13 +1634,13 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1916
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -1658,13 +1652,13 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -1682,19 +1676,20 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t xml:space="preserve">02
+</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -1717,7 +1712,7 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
@@ -1747,13 +1742,13 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
@@ -1773,7 +1768,7 @@
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
@@ -1785,61 +1780,51 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
-</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>084</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="n"/>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">916
+</t>
+        </is>
+      </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -1851,7 +1836,7 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
@@ -1863,8 +1848,7 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
@@ -1875,13 +1859,12 @@
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
@@ -1897,7 +1880,12 @@
 </t>
         </is>
       </c>
-      <c r="Z11" s="3" t="n"/>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45
+</t>
+        </is>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1911,12 +1899,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
+      <c r="C12" s="3" t="n"/>
       <c r="D12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">264
@@ -1937,19 +1920,19 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">9 841
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -1961,13 +1944,13 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">046
+          <t xml:space="preserve">086
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -1979,7 +1962,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -1991,13 +1974,13 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">084
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -2015,13 +1998,13 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">613
 </t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -2033,25 +2016,25 @@
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
@@ -2077,7 +2060,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -2089,7 +2072,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">893
 </t>
         </is>
       </c>
@@ -2107,7 +2090,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -2119,25 +2102,25 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -2173,7 +2156,7 @@
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
@@ -2197,13 +2180,13 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -2220,7 +2203,12 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">299
@@ -2247,7 +2235,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -2259,13 +2247,13 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -2277,11 +2265,16 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="n"/>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">912
@@ -2308,13 +2301,13 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">582
 </t>
         </is>
       </c>
@@ -2326,7 +2319,7 @@
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
@@ -2344,7 +2337,7 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7172
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -2367,15 +2360,10 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
@@ -2387,7 +2375,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">2935
 </t>
         </is>
       </c>
@@ -2399,13 +2387,13 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">0179
 </t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -2417,8 +2405,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -2435,19 +2422,19 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">012
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -2465,7 +2452,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -2483,7 +2470,7 @@
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
@@ -2507,7 +2494,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
@@ -2527,54 +2514,49 @@
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19404
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>443</t>
+          <t xml:space="preserve">1123
+</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">481
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">015
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9513
+          <t xml:space="preserve">953
 </t>
         </is>
       </c>
@@ -2586,31 +2568,31 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4532
+          <t xml:space="preserve">8532
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11273
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
@@ -2622,36 +2604,45 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0182
-</t>
+          <t>382</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9848
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11246
-</t>
-        </is>
-      </c>
-      <c r="X16" s="3" t="n"/>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1246
+</t>
+        </is>
+      </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100646
-</t>
-        </is>
-      </c>
-      <c r="Z16" s="3" t="n"/>
+          <t xml:space="preserve">9708
+</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2668,25 +2659,24 @@
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -2704,27 +2694,32 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="n"/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -2736,7 +2731,7 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2518
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -2748,25 +2743,25 @@
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2353
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -2784,11 +2779,16 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">822
+</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">20
 </t>
         </is>
       </c>
-      <c r="Z17" s="3" t="n"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2805,49 +2805,45 @@
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -2862,22 +2858,27 @@
 </t>
         </is>
       </c>
-      <c r="N18" s="3" t="n"/>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">2912
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">0 2
 </t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>892</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
@@ -2894,13 +2895,13 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">542
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -2918,17 +2919,21 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">852
+</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">10
 </t>
         </is>
       </c>
-      <c r="Z18" s="3" t="n"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
           <t>11</t>
@@ -2944,13 +2949,13 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
@@ -2962,7 +2967,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -2974,12 +2979,13 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>469</t>
+          <t xml:space="preserve">154
+</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -3003,11 +3009,16 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="n"/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9
+</t>
+        </is>
+      </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">922
@@ -3046,7 +3057,7 @@
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3058,7 +3069,7 @@
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -3070,11 +3081,16 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">06
 </t>
         </is>
       </c>
-      <c r="Z19" s="3" t="n"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -3088,16 +3104,21 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 8
+</t>
+        </is>
+      </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -3109,7 +3130,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">0596
 </t>
         </is>
       </c>
@@ -3133,31 +3154,26 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="n"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
@@ -3181,13 +3197,13 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -3199,7 +3215,7 @@
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -3211,7 +3227,7 @@
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">1232
 </t>
         </is>
       </c>
@@ -3221,7 +3237,11 @@
 </t>
         </is>
       </c>
-      <c r="Z20" s="3" t="n"/>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -3235,10 +3255,16 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">289
+</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3249,7 +3275,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -3261,7 +3287,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -3279,7 +3305,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">738
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -3310,13 +3336,13 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -3328,36 +3354,46 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">883
+          <t xml:space="preserve">887
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">219
 </t>
         </is>
       </c>
-      <c r="X21" s="3" t="n"/>
       <c r="Y21" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">903
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">08
 </t>
         </is>
       </c>
-      <c r="Z21" s="3" t="n"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -3371,21 +3407,27 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>374</t>
+          <t xml:space="preserve">294
+</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2328
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -3409,7 +3451,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -3421,25 +3463,25 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
+          <t xml:space="preserve">9912
 </t>
         </is>
       </c>
@@ -3451,13 +3493,13 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -3469,7 +3511,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89562
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
@@ -3481,29 +3523,34 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">226
 </t>
         </is>
       </c>
-      <c r="X22" s="3" t="inlineStr">
+      <c r="Y22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">802
 </t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">947
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="3" t="n"/>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -3520,7 +3567,7 @@
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1944
+          <t xml:space="preserve">19426
 </t>
         </is>
       </c>
@@ -3532,36 +3579,37 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">1122
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>522</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>97</t>
+          <t xml:space="preserve">287
+</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -3572,19 +3620,20 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">19529
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>431</t>
+          <t xml:space="preserve">9512
+</t>
         </is>
       </c>
       <c r="P23" s="3" t="n"/>
@@ -3596,53 +3645,58 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1079
+          <t xml:space="preserve">1072
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3602
+          <t xml:space="preserve">360
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">479
+          <t xml:space="preserve">377
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1086
+          <t xml:space="preserve">1084
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">1026
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0949278
+          <t xml:space="preserve">1987
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="Z23" s="3" t="n"/>
+          <t xml:space="preserve">94256
+</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3656,7 +3710,12 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">285
@@ -3689,38 +3748,48 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1656
+</t>
+        </is>
+      </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2186
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="n"/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5812
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -3732,19 +3801,19 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28239
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">782
+          <t xml:space="preserve">723
 </t>
         </is>
       </c>
@@ -3756,7 +3825,7 @@
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">8217
 </t>
         </is>
       </c>
@@ -3766,14 +3835,24 @@
 </t>
         </is>
       </c>
-      <c r="X24" s="3" t="n"/>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">25
 </t>
         </is>
       </c>
-      <c r="Z24" s="3" t="n"/>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">858
+</t>
+        </is>
+      </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3787,88 +3866,91 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">298
+</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1187
+</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">243
+</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>4441</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1129
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1
 </t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>424</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="n"/>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">592
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -3879,12 +3961,13 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>87</t>
+          <t xml:space="preserve">312
+</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
@@ -3896,19 +3979,18 @@
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8713
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">693
 </t>
         </is>
       </c>
@@ -3926,16 +4008,21 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1116
+</t>
+        </is>
+      </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2986
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -3947,7 +4034,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
@@ -3971,26 +4058,31 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="n"/>
+          <t xml:space="preserve">19896
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -4008,13 +4100,13 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -4032,29 +4124,34 @@
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">213
 </t>
         </is>
       </c>
-      <c r="W26" s="3" t="inlineStr">
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">862
+</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">245
 </t>
         </is>
       </c>
-      <c r="X26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">862
-</t>
-        </is>
-      </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="Z26" s="3" t="n"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -4089,7 +4186,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -4101,19 +4198,19 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -4125,19 +4222,19 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">9222
 </t>
         </is>
       </c>
@@ -4149,13 +4246,13 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -4173,30 +4270,40 @@
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">214
 </t>
         </is>
       </c>
-      <c r="W27" s="3" t="n"/>
       <c r="X27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">240
+</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">802
 </t>
         </is>
       </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">56
-</t>
-        </is>
-      </c>
-      <c r="Z27" s="3" t="n"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -4213,13 +4320,13 @@
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">2327
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -4231,7 +4338,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -4255,60 +4362,61 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>09</t>
+          <t xml:space="preserve">03
+</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12724
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">500
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">402
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -4320,28 +4428,34 @@
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2228
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">534
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>856</t>
-        </is>
-      </c>
-      <c r="Z28" s="3" t="n"/>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">532
+</t>
+        </is>
+      </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -4370,31 +4484,31 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -4410,21 +4524,22 @@
 </t>
         </is>
       </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="n"/>
+      <c r="M29" s="3" t="n"/>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>407</t>
+          <t xml:space="preserve">902
+</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4442,7 +4557,7 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -4460,29 +4575,34 @@
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">862
+</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">201
 </t>
         </is>
       </c>
-      <c r="W29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="X29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">862
-</t>
-        </is>
-      </c>
-      <c r="Y29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="Z29" s="3" t="n"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -4499,25 +4619,25 @@
       <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1494
+          <t xml:space="preserve">14984
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">1896
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">588
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -4535,32 +4655,32 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">2925
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">961
+          <t xml:space="preserve">3921
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="n"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>453</t>
+          <t xml:space="preserve">451
+</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -4577,7 +4697,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1127
+          <t xml:space="preserve">1129
 </t>
         </is>
       </c>
@@ -4601,28 +4721,33 @@
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1041
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t xml:space="preserve">3122
+</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
-</t>
-        </is>
-      </c>
-      <c r="Z30" s="3" t="n"/>
+          <t xml:space="preserve">524
+</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4645,7 +4770,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -4657,13 +4782,13 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -4675,14 +4800,14 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -4694,7 +4819,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
@@ -4712,25 +4837,25 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">641
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
@@ -4742,29 +4867,34 @@
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">773
+          <t xml:space="preserve">7478
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
-</t>
-        </is>
-      </c>
-      <c r="Z31" s="3" t="n"/>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -4778,22 +4908,26 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n"/>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>348</t>
+          <t xml:space="preserve">12328
+</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -4804,19 +4938,18 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -4826,35 +4959,34 @@
 </t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
+      <c r="L32" s="3" t="n"/>
       <c r="M32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="N32" s="3" t="n"/>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
@@ -4871,7 +5003,7 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">352
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -4883,7 +5015,7 @@
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -4895,11 +5027,15 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
-        </is>
-      </c>
-      <c r="Y32" s="3" t="n"/>
+          <t>853</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
       <c r="Z32" s="3" t="n"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -4914,10 +5050,16 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n"/>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+</t>
+        </is>
+      </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">926
+</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -4964,20 +5106,20 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="n"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -4995,7 +5137,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -5007,41 +5149,46 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">290
+</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">803
+</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">150
 </t>
         </is>
       </c>
-      <c r="V33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
-      <c r="W33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">274
-</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">803
-</t>
-        </is>
-      </c>
-      <c r="Y33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="Z33" s="3" t="n"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -5064,13 +5211,13 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -5082,7 +5229,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">4180
 </t>
         </is>
       </c>
@@ -5100,7 +5247,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -5112,7 +5259,7 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1919
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -5124,19 +5271,19 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -5154,13 +5301,13 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -5184,11 +5331,16 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
-</t>
-        </is>
-      </c>
-      <c r="Z34" s="3" t="n"/>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -5202,7 +5354,12 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n"/>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">304
@@ -5253,25 +5410,25 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1724
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
@@ -5283,7 +5440,7 @@
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
@@ -5301,7 +5458,7 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1922
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
@@ -5335,7 +5492,12 @@
 </t>
         </is>
       </c>
-      <c r="Z35" s="3" t="n"/>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">336
+</t>
+        </is>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -5352,13 +5514,14 @@
       <c r="C36" s="3" t="n"/>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">9336
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t xml:space="preserve">190
+</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -5387,7 +5550,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -5399,25 +5562,31 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
-</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="n"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>707</t>
+          <t xml:space="preserve">902
+</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -5429,7 +5598,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">2350
 </t>
         </is>
       </c>
@@ -5441,13 +5610,13 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">482
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
@@ -5465,7 +5634,7 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">852
 </t>
         </is>
       </c>
@@ -5475,7 +5644,12 @@
 </t>
         </is>
       </c>
-      <c r="Z36" s="3" t="n"/>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -5498,7 +5672,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">19295
 </t>
         </is>
       </c>
@@ -5510,14 +5684,13 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0694
+          <t xml:space="preserve">694
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>846</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -5528,7 +5701,7 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -5540,31 +5713,31 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">9511
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9502
+          <t xml:space="preserve">1502
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -5576,43 +5749,43 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">1173
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12304
+          <t xml:space="preserve">1204
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">1013
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1299
+          <t xml:space="preserve">1259
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">73672
 </t>
         </is>
       </c>
@@ -5622,7 +5795,12 @@
 </t>
         </is>
       </c>
-      <c r="Z37" s="3" t="n"/>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2473
+</t>
+        </is>
+      </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -5651,7 +5829,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -5675,31 +5853,32 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>468</t>
+          <t xml:space="preserve">178
+</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">909
 </t>
         </is>
       </c>
@@ -5717,53 +5896,58 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">7235
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">822
+</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">149
 </t>
         </is>
       </c>
-      <c r="U38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="V38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="W38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="X38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="Y38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74
-</t>
-        </is>
-      </c>
-      <c r="Z38" s="3" t="n"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -5780,37 +5964,35 @@
       <c r="C39" s="3" t="n"/>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>453</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>454</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -5822,26 +6004,26 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">602
 </t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1490
 </t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7960
+          <t xml:space="preserve">796
 </t>
         </is>
       </c>
@@ -5859,48 +6041,57 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">426
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">220
 </t>
         </is>
       </c>
-      <c r="W39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="X39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="Y39" s="3" t="n"/>
-      <c r="Z39" s="3" t="n"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -5914,7 +6105,12 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n"/>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">325
@@ -5929,7 +6125,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">854
 </t>
         </is>
       </c>
@@ -5941,7 +6137,7 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -5953,13 +6149,13 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">510
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5971,13 +6167,13 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -5995,13 +6191,13 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2312
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2822
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -6013,22 +6209,22 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">472
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">228
 </t>
         </is>
       </c>
-      <c r="V40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">286
-</t>
-        </is>
-      </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">258
@@ -6037,7 +6233,7 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -6047,7 +6243,12 @@
 </t>
         </is>
       </c>
-      <c r="Z40" s="3" t="n"/>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8262
+</t>
+        </is>
+      </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
           <t>27</t>
@@ -6064,13 +6265,13 @@
       <c r="C41" s="3" t="n"/>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179 0
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -6088,14 +6289,13 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -6106,13 +6306,13 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">2091
 </t>
         </is>
       </c>
@@ -6125,14 +6325,19 @@
       <c r="N41" s="3" t="n"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
-</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="n"/>
+          <t xml:space="preserve">812
+</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">016
+</t>
+        </is>
+      </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
@@ -6150,30 +6355,31 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">378
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">212
+</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">682
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -6183,7 +6389,12 @@
 </t>
         </is>
       </c>
-      <c r="Z41" s="3" t="n"/>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -6198,33 +6409,28 @@
         </is>
       </c>
       <c r="C42" s="3" t="n"/>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D42" s="3" t="n"/>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">324
 </t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1828
-</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">256
 </t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -6236,73 +6442,88 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1728
+</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">820
+</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">86
 </t>
         </is>
       </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1984
-</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="n"/>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">922
-</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="R42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">820
-</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">276
-</t>
-        </is>
-      </c>
-      <c r="T42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 14
-</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="V42" s="3" t="n"/>
-      <c r="W42" s="3" t="n"/>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
       <c r="X42" s="3" t="n"/>
       <c r="Y42" s="3" t="n"/>
       <c r="Z42" s="3" t="n"/>
@@ -6418,58 +6639,55 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
+          <t xml:space="preserve">1020
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">547
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
-</t>
+          <t>698</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">91
+</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>056</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1411
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1119
+</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="n"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">23662
 </t>
         </is>
       </c>
@@ -6479,10 +6697,15 @@
 </t>
         </is>
       </c>
-      <c r="Q45" s="3" t="n"/>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1069
+</t>
+        </is>
+      </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">1027
 </t>
         </is>
       </c>
@@ -6494,19 +6717,19 @@
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">1327
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">8927
 </t>
         </is>
       </c>
@@ -6518,17 +6741,22 @@
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2212
+          <t xml:space="preserve">193272
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="3" t="n"/>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -6545,28 +6773,28 @@
       <c r="C46" s="3" t="n"/>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">323
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">255
 </t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">175
@@ -6575,37 +6803,37 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1041
+          <t xml:space="preserve">1307
 </t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1427
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -6617,55 +6845,65 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">02
 </t>
         </is>
       </c>
-      <c r="Q46" s="3" t="n"/>
       <c r="R46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">257
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">229
 </t>
         </is>
       </c>
-      <c r="S46" s="3" t="n"/>
       <c r="T46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">602
 </t>
         </is>
       </c>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">823
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">872085
-</t>
-        </is>
-      </c>
-      <c r="Z46" s="3" t="n"/>
+      <c r="Y46" s="3" t="n"/>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 9929
+</t>
+        </is>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/508/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/508/original_transcribed_data.xlsx
@@ -729,122 +729,102 @@
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">397
-</t>
+          <t>317</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>914</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="X4" s="3" t="n"/>
@@ -866,140 +846,117 @@
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>916</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">702
-</t>
+          <t>702</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1018,140 +975,117 @@
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
-</t>
+          <t>322</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9212
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3906
-</t>
+          <t>506</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>772</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1170,62 +1104,52 @@
       <c r="C7" s="3" t="n"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2305
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1235,74 +1159,62 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>872</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
-</t>
+          <t>742</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1321,14 +1233,12 @@
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -1338,117 +1248,98 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7912
-</t>
+          <t>916</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1467,8 +1358,7 @@
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1479
-</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1478,14 +1368,12 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
-</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">578
-</t>
+          <t>578</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -1495,92 +1383,77 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">441
-</t>
+          <t>441</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
-</t>
+          <t>926</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39726
-</t>
+          <t>926</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4512
-</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1294
-</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
-</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
-</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3186
-</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
-</t>
+          <t>488</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
-</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
@@ -1590,14 +1463,12 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3826
-</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1616,140 +1487,117 @@
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>640</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1768,33 +1616,28 @@
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J11" s="3" t="n"/>
@@ -1806,44 +1649,37 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
-</t>
+          <t>916</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -1853,8 +1689,7 @@
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
@@ -1864,26 +1699,22 @@
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>812</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1902,140 +1733,117 @@
       <c r="C12" s="3" t="n"/>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 841
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">086
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">084
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">613
-</t>
+          <t>672</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>812</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>832</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2054,140 +1862,117 @@
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">893
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>842</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2205,146 +1990,122 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>1 01</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">582
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>772</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">514
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2363,44 +2124,37 @@
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2935
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -2410,92 +2164,77 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">582
-</t>
+          <t>582</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2514,20 +2253,17 @@
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -2537,69 +2273,58 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
-</t>
+          <t>875</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
-</t>
+          <t>953</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
-</t>
+          <t>946</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8532
-</t>
+          <t>532</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
-</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
-</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
-</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
@@ -2609,38 +2334,32 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
-</t>
+          <t>492</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
-</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9708
-</t>
+          <t>088</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2656,17 +2375,19 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -2676,117 +2397,98 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>642</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>822</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2825,20 +2527,17 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -2848,32 +2547,27 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2912
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 2
-</t>
+          <t>0 2</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -2883,38 +2577,32 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">542
-</t>
+          <t>542</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
@@ -2924,14 +2612,12 @@
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
-</t>
+          <t>852</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2949,146 +2635,122 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>878</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3106,135 +2768,113 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 8
-</t>
+          <t>1 01</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0596
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="N20" s="3" t="n"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
-</t>
+          <t>992</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
-</t>
+          <t>852</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
@@ -3257,141 +2897,122 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="n"/>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">887
-</t>
+          <t>882</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">903
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3409,146 +3030,122 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9912
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>562</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
-</t>
+          <t>802</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3567,20 +3164,17 @@
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19426
-</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>904</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -3590,111 +3184,93 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>838</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>517</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">939
-</t>
+          <t>932</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19529
-</t>
+          <t>929</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9512
-</t>
+          <t>4582</t>
         </is>
       </c>
       <c r="P23" s="3" t="n"/>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
-</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1072
-</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">360
-</t>
+          <t>360</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">377
-</t>
+          <t>377</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1084
-</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1026
-</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1987
-</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94256
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3712,44 +3288,37 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -3759,98 +3328,82 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1656
-</t>
+          <t>99919991</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3869,20 +3422,17 @@
       <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -3892,14 +3442,12 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -3909,38 +3457,32 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -3955,26 +3497,22 @@
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>712</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
@@ -3984,14 +3522,12 @@
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">693
-</t>
+          <t>672</t>
         </is>
       </c>
       <c r="Z25" s="3" t="n"/>
@@ -4010,146 +3546,122 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19896
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4168,140 +3680,117 @@
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9222
-</t>
+          <t>982</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">632
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
-</t>
+          <t>802</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4320,140 +3809,117 @@
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2327
-</t>
+          <t>327</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>928</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>402</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">532
-</t>
+          <t>532</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4472,135 +3938,113 @@
       <c r="C29" s="3" t="n"/>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M29" s="3" t="n"/>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>906</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4619,44 +4063,37 @@
       <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14984
-</t>
+          <t>1484</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1896
-</t>
+          <t>896</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>588</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">806
-</t>
+          <t>806</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
@@ -4666,81 +4103,68 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2925
-</t>
+          <t>925</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3921
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="N30" s="3" t="n"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">451
-</t>
+          <t>457</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1307
-</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
-</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3222
-</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1041
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
-</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3122
-</t>
+          <t>3722</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">524
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4764,135 +4188,113 @@
       <c r="C31" s="3" t="n"/>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
-</t>
+          <t>642</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7478
-</t>
+          <t>778</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -4910,14 +4312,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12328
-</t>
+          <t>388</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -4932,14 +4332,12 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -4949,39 +4347,33 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="L32" s="3" t="n"/>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>916</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -4991,38 +4383,32 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>358</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
@@ -5032,8 +4418,7 @@
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="Z32" s="3" t="n"/>
@@ -5052,141 +4437,118 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>946</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N33" s="3" t="n"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
+          <t>782</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">803
-</t>
+          <t>802</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5202,143 +4564,124 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n"/>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>872</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
-</t>
+          <t>672</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
-</t>
+          <t>863</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5356,146 +4699,122 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
-</t>
+          <t>628</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">336
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5514,140 +4833,117 @@
       <c r="C36" s="3" t="n"/>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9336
-</t>
+          <t>936</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2350
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">482
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
-</t>
+          <t>552</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5666,26 +4962,22 @@
       <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1615
-</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19295
-</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
-</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
-</t>
+          <t>694</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -5695,110 +4987,92 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9499
-</t>
+          <t>491</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9511
-</t>
+          <t>951</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1502
-</t>
+          <t>502</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
-</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1173
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
-</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1013
-</t>
+          <t>703</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
-</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
-</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
-</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73672
-</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">372
-</t>
+          <t>372</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2473
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5817,135 +5091,117 @@
       <c r="C38" s="3" t="n"/>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>923</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="n"/>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
+      </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
-</t>
+          <t>909</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>732</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -5964,8 +5220,7 @@
       <c r="C39" s="3" t="n"/>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -5975,8 +5230,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -5986,93 +5240,78 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">602
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1490
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">796
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
-</t>
+          <t>612</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>241 7</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
@@ -6082,14 +5321,12 @@
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6107,146 +5344,122 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
-</t>
+          <t>325</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">472
-</t>
+          <t>472</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8262
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6265,32 +5478,27 @@
       <c r="C41" s="3" t="n"/>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -6300,99 +5508,83 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="N41" s="3" t="n"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">378
-</t>
+          <t>592</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6412,116 +5604,97 @@
       <c r="D42" s="3" t="n"/>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="X42" s="3" t="n"/>
@@ -6542,8 +5715,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D43" s="3" t="n"/>
@@ -6584,8 +5756,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
@@ -6627,26 +5798,22 @@
       <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
-</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>746</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
-</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">547
-</t>
+          <t>547</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
@@ -6656,105 +5823,88 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
-</t>
+          <t>746</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="N45" s="3" t="n"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23662
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1069
-</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1027
-</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2412
-</t>
+          <t>2418</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1327
-</t>
+          <t>387</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>953</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8927
-</t>
+          <t>857</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">963
-</t>
+          <t>963</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193272
-</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -6773,135 +5923,113 @@
       <c r="C46" s="3" t="n"/>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
-</t>
+          <t>323</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1307
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">602
-</t>
+          <t>602</t>
         </is>
       </c>
       <c r="Y46" s="3" t="n"/>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 9929
-</t>
+          <t>0 22</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/508/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/508/original_transcribed_data.xlsx
@@ -779,12 +779,12 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>211</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>298</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>452</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>218</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>201</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>281</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>65</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>128</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>372</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>222</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
@@ -1284,7 +1284,7 @@
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>162</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>196</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>00</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1537,12 +1537,12 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>2913</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>642</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
@@ -1637,7 +1637,7 @@
       <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J11" s="3" t="n"/>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>2 81</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>242</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>742</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>1 01</t>
+          <t>0 1 01</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>165</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>82</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>262</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>582</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>742</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>86</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>107</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>853</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>03</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>815</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>173</t>
         </is>
       </c>
       <c r="K16" s="3" t="n"/>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2314,12 +2314,12 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -2334,17 +2334,17 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>412</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>088</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -2412,23 +2412,23 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>191</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>221</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>125</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>249</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>166</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>196</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>101</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>812</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>1 01</t>
+          <t>0 01</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>296</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>262</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>297</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>109</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>253</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -2897,12 +2897,12 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>289</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>191</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>282</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>219</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>81</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>199</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
@@ -3164,7 +3164,7 @@
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -3199,12 +3199,12 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>317</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>931</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -3214,12 +3214,12 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>81</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>4582</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="P23" s="3" t="n"/>
@@ -3235,17 +3235,17 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>347</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>99919991</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>214</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>856</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>231</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>296</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>184</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>02</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -3596,17 +3596,17 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>296</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>293</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>180</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>182</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>01</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>159</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>162</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>188</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>000</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>301</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>122</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
@@ -3904,12 +3904,12 @@
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>278</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>145</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>206</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -4108,13 +4108,13 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>921</t>
         </is>
       </c>
       <c r="N30" s="3" t="n"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>451</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -4139,17 +4139,17 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>2222</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -4224,7 +4224,7 @@
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>189</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>240</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -4312,12 +4312,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>328</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>175</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
@@ -4363,12 +4363,12 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>876</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>221</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>253</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -4493,7 +4493,7 @@
       <c r="N33" s="3" t="n"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>903</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>248</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>482</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>262</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>803</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>08</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>238</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>244</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>286</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>122</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>254</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>532</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -4833,7 +4833,7 @@
       <c r="C36" s="3" t="n"/>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>336</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>156</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>86</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>442</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
@@ -5007,22 +5007,22 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>92</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>08</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>86</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5091,7 +5091,7 @@
       <c r="C38" s="3" t="n"/>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>223</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>254</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>011</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>186</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>492</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>76</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
@@ -5265,13 +5265,13 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>190</t>
         </is>
       </c>
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>966</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>251</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>241 7</t>
+          <t>241 0</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -5394,12 +5394,12 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>298</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>312</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>196</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>258</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>216</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>269</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>828</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>822</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>136</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -5649,52 +5649,52 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
           <t>01</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="R42" s="3" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="T42" s="3" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="V42" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X42" s="3" t="n"/>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>346</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>146</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>111</t>
         </is>
       </c>
       <c r="N45" s="3" t="n"/>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>963</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>822</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -5923,7 +5923,7 @@
       <c r="C46" s="3" t="n"/>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -5958,12 +5958,12 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>99</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>124</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -5973,42 +5973,42 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>223</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="T46" s="3" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>298</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
@@ -6026,10 +6026,14 @@
           <t>602</t>
         </is>
       </c>
-      <c r="Y46" s="3" t="n"/>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t>2 1</t>
+        </is>
+      </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t>0 22</t>
+          <t>00 2989</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/508/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/508/original_transcribed_data.xlsx
@@ -784,7 +784,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>914</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>238</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>208</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
@@ -921,12 +921,12 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>231</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>70</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>198</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>772</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>223</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>70</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>104</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>108</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>00</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>00</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -1637,7 +1637,7 @@
       <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J11" s="3" t="n"/>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>818</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
@@ -1788,17 +1788,17 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>905</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>243</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
@@ -1813,12 +1813,12 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>67</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>818</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>74</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>0 1 01</t>
+          <t>0 01</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>08</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>268</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>919</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>207</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>875</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>143</t>
         </is>
       </c>
       <c r="K16" s="3" t="n"/>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>353</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>109</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>114</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>100</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>7088</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>175</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>02</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>82</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>18</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -2680,22 +2680,22 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>193</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>85</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>928</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>90</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>878</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>0 01</t>
+          <t>0 0</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>853</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -2897,12 +2897,12 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>288</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>00</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>88</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
@@ -3002,12 +3002,12 @@
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>90</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>139</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>286</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -3164,7 +3164,7 @@
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -3214,12 +3214,12 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>457</t>
         </is>
       </c>
       <c r="P23" s="3" t="n"/>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -3240,12 +3240,12 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>360</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>577</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>812</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>20</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>788</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>673</t>
         </is>
       </c>
       <c r="Z25" s="3" t="n"/>
@@ -3546,67 +3546,67 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
           <t>296</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>918</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -3621,17 +3621,17 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>233</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>08</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>76</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>868</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>188</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>988</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>63</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>000</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>200</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>2162</t>
+          <t>212</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>176</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
@@ -3984,7 +3984,7 @@
       <c r="M29" s="3" t="n"/>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>868</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>118</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -4108,13 +4108,13 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>92</t>
         </is>
       </c>
       <c r="N30" s="3" t="n"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>457</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -4149,17 +4149,17 @@
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>104</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>3828</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>179</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>181</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -4224,7 +4224,7 @@
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>185</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>280</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>263</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>84</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>258</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>146</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
@@ -4493,7 +4493,7 @@
       <c r="N33" s="3" t="n"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>803</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>278</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
@@ -4518,17 +4518,17 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>78</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>242</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>290</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>09</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>876</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>86</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>274</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>180</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -4754,17 +4754,17 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>92</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>257</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
@@ -4878,17 +4878,17 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>155</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>928</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -5007,17 +5007,17 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>99</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>190</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>256</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -5126,37 +5126,37 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>000</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>28</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>886</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>49</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>70</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -5271,7 +5271,7 @@
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>95</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -5394,17 +5394,17 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>92</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>194</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>286</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>869</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>598</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>828</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -5649,7 +5649,7 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>148</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>28</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D43" s="3" t="n"/>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>746</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -5838,18 +5838,18 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>976</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>311</t>
         </is>
       </c>
       <c r="N45" s="3" t="n"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>241</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
@@ -5879,22 +5879,22 @@
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
           <t>963</t>
         </is>
       </c>
-      <c r="V45" s="3" t="inlineStr">
-        <is>
-          <t>857</t>
-        </is>
-      </c>
-      <c r="W45" s="3" t="inlineStr">
-        <is>
-          <t>963</t>
-        </is>
-      </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>327</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -5948,42 +5948,42 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>92</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>261</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>97</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
@@ -6026,14 +6026,10 @@
           <t>602</t>
         </is>
       </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t>2 1</t>
-        </is>
-      </c>
+      <c r="Y46" s="3" t="n"/>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t>00 2989</t>
+          <t>0 2989</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">
